--- a/S_数据表/Talent_Template.xlsx
+++ b/S_数据表/Talent_Template.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4319,7 +4319,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="44">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4513,22 +4513,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4616,14 +4601,14 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4632,7 +4617,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="80">
+  <fills count="64">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4941,42 +4926,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399914548173467"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5044,66 +4993,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399945066682943"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5415,58 +5304,76 @@
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5487,101 +5394,83 @@
     <xf numFmtId="0" fontId="26" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="68" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="69" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="70" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="73" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="74" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="75" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="76" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="77" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="78" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="79" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="79" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -5808,7 +5697,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{05EDE834-5FF5-4FE4-87C2-BF439A39F370}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{574BBCEC-14A9-40F1-9CAB-62709A68D590}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -12459,7 +12348,7 @@
         <v>451</v>
       </c>
       <c r="D138" s="2">
-        <v>104101</v>
+        <v>401101</v>
       </c>
       <c r="E138" s="2">
         <v>1</v>
@@ -12504,7 +12393,7 @@
         <v>456</v>
       </c>
       <c r="D139" s="2">
-        <v>112301</v>
+        <v>402101</v>
       </c>
       <c r="E139" s="2">
         <v>1</v>
@@ -12549,7 +12438,7 @@
         <v>460</v>
       </c>
       <c r="D140" s="2">
-        <v>102201</v>
+        <v>402201</v>
       </c>
       <c r="E140" s="2">
         <v>1</v>
@@ -12594,7 +12483,7 @@
         <v>463</v>
       </c>
       <c r="D141" s="2">
-        <v>102301</v>
+        <v>402301</v>
       </c>
       <c r="E141" s="2">
         <v>1</v>
@@ -12639,7 +12528,7 @@
         <v>466</v>
       </c>
       <c r="D142" s="2">
-        <v>105101</v>
+        <v>403101</v>
       </c>
       <c r="E142" s="2">
         <v>1</v>
@@ -12686,7 +12575,7 @@
         <v>467</v>
       </c>
       <c r="D143" s="2">
-        <v>105101</v>
+        <v>403201</v>
       </c>
       <c r="E143" s="2">
         <v>1</v>
@@ -12733,7 +12622,7 @@
         <v>471</v>
       </c>
       <c r="D144" s="2">
-        <v>202101</v>
+        <v>404101</v>
       </c>
       <c r="E144" s="2">
         <v>1</v>
@@ -12778,7 +12667,7 @@
         <v>475</v>
       </c>
       <c r="D145" s="2">
-        <v>114201</v>
+        <v>404201</v>
       </c>
       <c r="E145" s="2">
         <v>1</v>
@@ -12825,7 +12714,7 @@
         <v>479</v>
       </c>
       <c r="D146" s="2">
-        <v>104301</v>
+        <v>404301</v>
       </c>
       <c r="E146" s="2">
         <v>1</v>
@@ -12872,7 +12761,7 @@
         <v>482</v>
       </c>
       <c r="D147" s="2">
-        <v>104401</v>
+        <v>404401</v>
       </c>
       <c r="E147" s="2">
         <v>1</v>
@@ -12919,7 +12808,7 @@
         <v>486</v>
       </c>
       <c r="D148" s="2">
-        <v>104501</v>
+        <v>404501</v>
       </c>
       <c r="E148" s="2">
         <v>1</v>
@@ -12966,7 +12855,7 @@
         <v>489</v>
       </c>
       <c r="D149" s="2">
-        <v>105101</v>
+        <v>405101</v>
       </c>
       <c r="E149" s="2">
         <v>1</v>
@@ -13013,7 +12902,7 @@
         <v>89</v>
       </c>
       <c r="D150" s="2">
-        <v>105201</v>
+        <v>405201</v>
       </c>
       <c r="E150" s="2">
         <v>1</v>
@@ -13058,7 +12947,7 @@
         <v>94</v>
       </c>
       <c r="D151" s="2">
-        <v>106101</v>
+        <v>406101</v>
       </c>
       <c r="E151" s="2">
         <v>1</v>
@@ -13105,7 +12994,7 @@
         <v>97</v>
       </c>
       <c r="D152" s="2">
-        <v>106201</v>
+        <v>406201</v>
       </c>
       <c r="E152" s="2">
         <v>1</v>
@@ -13150,7 +13039,7 @@
         <v>102</v>
       </c>
       <c r="D153" s="2">
-        <v>106301</v>
+        <v>406301</v>
       </c>
       <c r="E153" s="2">
         <v>1</v>
@@ -13197,7 +13086,7 @@
         <v>504</v>
       </c>
       <c r="D154" s="2">
-        <v>105101</v>
+        <v>406401</v>
       </c>
       <c r="E154" s="2">
         <v>1</v>
@@ -13244,7 +13133,7 @@
         <v>112</v>
       </c>
       <c r="D155" s="2">
-        <v>106501</v>
+        <v>406501</v>
       </c>
       <c r="E155" s="2">
         <v>1</v>
@@ -13291,7 +13180,7 @@
         <v>510</v>
       </c>
       <c r="D156" s="2">
-        <v>205201</v>
+        <v>407101</v>
       </c>
       <c r="E156" s="2">
         <v>1</v>
@@ -13336,7 +13225,7 @@
         <v>120</v>
       </c>
       <c r="D157" s="2">
-        <v>107201</v>
+        <v>407201</v>
       </c>
       <c r="E157" s="2">
         <v>1</v>
@@ -13383,7 +13272,7 @@
         <v>518</v>
       </c>
       <c r="D158" s="2">
-        <v>205201</v>
+        <v>407301</v>
       </c>
       <c r="E158" s="2">
         <v>1</v>
@@ -13428,7 +13317,7 @@
         <v>131</v>
       </c>
       <c r="D159" s="2">
-        <v>108101</v>
+        <v>408101</v>
       </c>
       <c r="E159" s="2">
         <v>1</v>
@@ -13475,7 +13364,7 @@
         <v>523</v>
       </c>
       <c r="D160" s="2">
-        <v>111101</v>
+        <v>411101</v>
       </c>
       <c r="E160" s="2">
         <v>2</v>
@@ -13520,7 +13409,7 @@
         <v>489</v>
       </c>
       <c r="D161" s="2">
-        <v>105101</v>
+        <v>412101</v>
       </c>
       <c r="E161" s="2">
         <v>2</v>
@@ -13565,7 +13454,7 @@
         <v>530</v>
       </c>
       <c r="D162" s="2">
-        <v>112201</v>
+        <v>412201</v>
       </c>
       <c r="E162" s="2">
         <v>2</v>
@@ -13612,7 +13501,7 @@
         <v>463</v>
       </c>
       <c r="D163" s="2">
-        <v>112301</v>
+        <v>412301</v>
       </c>
       <c r="E163" s="2">
         <v>2</v>
@@ -13657,7 +13546,7 @@
         <v>535</v>
       </c>
       <c r="D164" s="2">
-        <v>111101</v>
+        <v>413101</v>
       </c>
       <c r="E164" s="2">
         <v>2</v>
@@ -13702,7 +13591,7 @@
         <v>539</v>
       </c>
       <c r="D165" s="2">
-        <v>111101</v>
+        <v>413201</v>
       </c>
       <c r="E165" s="2">
         <v>2</v>
@@ -13747,7 +13636,7 @@
         <v>543</v>
       </c>
       <c r="D166" s="2">
-        <v>114101</v>
+        <v>414101</v>
       </c>
       <c r="E166" s="2">
         <v>2</v>
@@ -13792,7 +13681,7 @@
         <v>546</v>
       </c>
       <c r="D167" s="2">
-        <v>214201</v>
+        <v>414201</v>
       </c>
       <c r="E167" s="2">
         <v>2</v>
@@ -13837,7 +13726,7 @@
         <v>550</v>
       </c>
       <c r="D168" s="2">
-        <v>114301</v>
+        <v>414301</v>
       </c>
       <c r="E168" s="2">
         <v>2</v>
@@ -13884,7 +13773,7 @@
         <v>530</v>
       </c>
       <c r="D169" s="2">
-        <v>213201</v>
+        <v>414401</v>
       </c>
       <c r="E169" s="2">
         <v>2</v>
@@ -13929,7 +13818,7 @@
         <v>555</v>
       </c>
       <c r="D170" s="2">
-        <v>114501</v>
+        <v>414501</v>
       </c>
       <c r="E170" s="2">
         <v>2</v>
@@ -13976,7 +13865,7 @@
         <v>530</v>
       </c>
       <c r="D171" s="2">
-        <v>115101</v>
+        <v>415101</v>
       </c>
       <c r="E171" s="2">
         <v>2</v>
@@ -14023,7 +13912,7 @@
         <v>530</v>
       </c>
       <c r="D172" s="2">
-        <v>115201</v>
+        <v>415201</v>
       </c>
       <c r="E172" s="2">
         <v>2</v>
@@ -14070,7 +13959,7 @@
         <v>563</v>
       </c>
       <c r="D173" s="2">
-        <v>116101</v>
+        <v>416101</v>
       </c>
       <c r="E173" s="2">
         <v>2</v>
@@ -14117,7 +14006,7 @@
         <v>566</v>
       </c>
       <c r="D174" s="2">
-        <v>116201</v>
+        <v>416201</v>
       </c>
       <c r="E174" s="2">
         <v>2</v>
@@ -14162,7 +14051,7 @@
         <v>563</v>
       </c>
       <c r="D175" s="2">
-        <v>214201</v>
+        <v>416301</v>
       </c>
       <c r="E175" s="2">
         <v>2</v>
@@ -14207,7 +14096,7 @@
         <v>555</v>
       </c>
       <c r="D176" s="2">
-        <v>116401</v>
+        <v>416401</v>
       </c>
       <c r="E176" s="2">
         <v>2</v>
@@ -14252,7 +14141,7 @@
         <v>575</v>
       </c>
       <c r="D177" s="2">
-        <v>116501</v>
+        <v>416501</v>
       </c>
       <c r="E177" s="2">
         <v>2</v>
@@ -14299,7 +14188,7 @@
         <v>579</v>
       </c>
       <c r="D178" s="2">
-        <v>312301</v>
+        <v>417101</v>
       </c>
       <c r="E178" s="2">
         <v>2</v>
@@ -14344,7 +14233,7 @@
         <v>582</v>
       </c>
       <c r="D179" s="2">
-        <v>317201</v>
+        <v>417201</v>
       </c>
       <c r="E179" s="2">
         <v>2</v>
@@ -14389,7 +14278,7 @@
         <v>585</v>
       </c>
       <c r="D180" s="2">
-        <v>117301</v>
+        <v>417301</v>
       </c>
       <c r="E180" s="2">
         <v>2</v>
@@ -14434,7 +14323,7 @@
         <v>589</v>
       </c>
       <c r="D181" s="2">
-        <v>118101</v>
+        <v>418101</v>
       </c>
       <c r="E181" s="2">
         <v>2</v>

--- a/S_数据表/Talent_Template.xlsx
+++ b/S_数据表/Talent_Template.xlsx
@@ -3886,7 +3886,7 @@
     <t>402101;402201;402301</t>
   </si>
   <si>
-    <t>裂地击暴击概率提升10%;裂地击暴击概率提升20;裂地击暴击概率提升30%</t>
+    <t>风影击暴击概率提升10%;风影击暴击概率提升20;风影击暴击概率提升30%</t>
   </si>
   <si>
     <t>SkillAdd,60013011,8,0.1;SkillAdd,60013012,8,0.1;SkillAdd,60013013,8,0.1;SkillAdd,60013014,8,0.1;SkillAdd,60013015,8,0.1|SkillAdd,60013011,8,0.2;SkillAdd,60013012,8,0.2;SkillAdd,60013013,8,0.2;SkillAdd,60013014,8,0.2;SkillAdd,60013015,8,0.2|SkillAdd,60013011,8,0.3;SkillAdd,60013012,8,0.3;SkillAdd,60013013,8,0.3;SkillAdd,60013014,8,0.3;SkillAdd,60013015,8,0.3</t>
@@ -3898,7 +3898,7 @@
     <t>Wind-induced dizziness</t>
   </si>
   <si>
-    <t>裂地击有对目标额外造成1秒眩晕;裂地击对目标额外造成1.5秒眩晕</t>
+    <t>风影击有对目标额外造成1秒眩晕;风影击对目标额外造成1.5秒眩晕</t>
   </si>
   <si>
     <t>SkillAdd,60013011,6,90003011;SkillAdd,60013012,6,90003011;SkillAdd,60013013,6,90003011;SkillAdd,60013014,6,90003011;SkillAdd,60013015,6,90003011|SkillAdd,60013011,6,90003033;SkillAdd,60013012,6,90003033;SkillAdd,60013013,6,90003033;SkillAdd,60013014,6,90003033;SkillAdd,60013015,6,90003033</t>
@@ -3913,13 +3913,13 @@
     <t>新增技能:神谕之手</t>
   </si>
   <si>
-    <t>裂地击能力</t>
+    <t>风影击能力</t>
   </si>
   <si>
     <t>Wind Shadow Strike Ability</t>
   </si>
   <si>
-    <t>裂地击的碎甲效果额外增加10%;裂地击的碎甲效果额外增加20%</t>
+    <t>风影击的碎甲效果额外增加10%;风影击的碎甲效果额外增加20%</t>
   </si>
   <si>
     <t>SkillAdd,60013011,6,90003019;SkillAdd,60013012,6,90003019;SkillAdd,60013013,6,90003019;SkillAdd,60013014,6,90003019;SkillAdd,60013015,6,90003019|SkillAdd,60013011,6,90003021;SkillAdd,60013012,6,90003021;SkillAdd,60013013,6,90003021;SkillAdd,60013014,6,90003021;SkillAdd,60013015,6,90003021</t>
@@ -4060,7 +4060,7 @@
     <t>Wind Shadow Strike</t>
   </si>
   <si>
-    <t>暴击时有4%概率直接触发裂地击技能;暴击时有8%概率直接触发裂地击技能;暴击时有12%概率直接触发裂地击技能</t>
+    <t>暴击时有4%概率直接触发风影击技能;暴击时有8%概率直接触发风影击技能;暴击时有12%概率直接触发风影击技能</t>
   </si>
   <si>
     <t>60040005;60040006;60040007</t>
@@ -4084,7 +4084,7 @@
     <t>Attack Trigger</t>
   </si>
   <si>
-    <t>攻击时有2%概率直接触发裂地击技能;攻击时有4%概率直接触发裂地击技能;攻击时有6%概率直接触发裂地击技能</t>
+    <t>攻击时有2%概率直接触发风影击技能;攻击时有4%概率直接触发风影击技能;攻击时有6%概率直接触发风影击技能</t>
   </si>
   <si>
     <t>60040008;60040009;60040010</t>
@@ -4123,7 +4123,7 @@
     <t>每次攻击有概率召唤自己的仆从协助自己战斗,仆从最多拥有10个</t>
   </si>
   <si>
-    <t>使用裂地击有概率降低目标20%移动速度,持续3秒;使用裂地击有概率降低目标40%移动速度,持续3秒;使用裂地击有概率降低目标60%移动速度,持续3秒</t>
+    <t>使用风影击有概率降低目标20%移动速度,持续3秒;使用风影击有概率降低目标40%移动速度,持续3秒;使用风影击有概率降低目标60%移动速度,持续3秒</t>
   </si>
   <si>
     <t>SkillAdd,60013011,6,90003016;SkillAdd,60013012,6,90003016;SkillAdd,60013013,6,90003016;SkillAdd,60013014,6,90003016;SkillAdd,60013015,6,90003016|SkillAdd,60013011,6,90003017;SkillAdd,60013012,6,90003017;SkillAdd,60013013,6,90003017;SkillAdd,60013014,6,90003017;SkillAdd,60013015,6,90003017|SkillAdd,60013011,6,90003018;SkillAdd,60013012,6,90003018;SkillAdd,60013013,6,90003018;SkillAdd,60013014,6,90003018;SkillAdd,60013015,6,90003018</t>
@@ -4608,12 +4608,12 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tahoma"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
+      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5697,7 +5697,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{574BBCEC-14A9-40F1-9CAB-62709A68D590}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{6B345C5A-5E98-40E1-B0B2-12AA3A7A43D7}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>

--- a/S_数据表/Talent_Template.xlsx
+++ b/S_数据表/Talent_Template.xlsx
@@ -1044,7 +1044,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="595">
   <si>
     <t>ID</t>
   </si>
@@ -1809,7 +1809,7 @@
     <t>攻击穿透</t>
   </si>
   <si>
-    <t xml:space="preserve"> Armor Penetration</t>
+    <t>Armor Penetration</t>
   </si>
   <si>
     <t>攻击穿透+2%;攻击穿透+4%;攻击穿透+6%;攻击穿透+8%;攻击穿透+10%</t>
@@ -2152,7 +2152,7 @@
     <t>药剂恢复</t>
   </si>
   <si>
-    <t xml:space="preserve"> Altered Mixture</t>
+    <t>Altered Mixture</t>
   </si>
   <si>
     <t>使用药剂恢复效果提升50%</t>
@@ -4028,6 +4028,9 @@
   </si>
   <si>
     <t>魔灵护盾</t>
+  </si>
+  <si>
+    <t>Magic Spirit Shield</t>
   </si>
   <si>
     <t>406201;406401;107201</t>
@@ -4601,6 +4604,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -4609,11 +4617,6 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Tahoma"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -5697,7 +5700,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{6B345C5A-5E98-40E1-B0B2-12AA3A7A43D7}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{6A4F19B7-6378-43C2-A831-56E464E4D2C8}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -13036,7 +13039,7 @@
         <v>500</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>102</v>
+        <v>501</v>
       </c>
       <c r="D153" s="2">
         <v>406301</v>
@@ -13060,10 +13063,10 @@
         <v>1</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L153" s="22" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M153" s="22" t="s">
         <v>105</v>
@@ -13080,10 +13083,10 @@
         <v>406401</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D154" s="2">
         <v>406401</v>
@@ -13110,13 +13113,13 @@
         <v>406501</v>
       </c>
       <c r="L154" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M154" s="22" t="s">
         <v>86</v>
       </c>
       <c r="N154" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O154" s="5">
         <v>0</v>
@@ -13127,7 +13130,7 @@
         <v>406501</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>112</v>
@@ -13157,7 +13160,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M155" s="22" t="s">
         <v>112</v>
@@ -13174,10 +13177,10 @@
         <v>407101</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D156" s="2">
         <v>407101</v>
@@ -13204,14 +13207,14 @@
         <v>0</v>
       </c>
       <c r="L156" s="22" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M156" s="22"/>
       <c r="N156" s="5">
         <v>0</v>
       </c>
       <c r="O156" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13219,7 +13222,7 @@
         <v>407201</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>120</v>
@@ -13246,10 +13249,10 @@
         <v>5</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L157" s="22" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M157" s="22" t="s">
         <v>123</v>
@@ -13258,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="O157" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="158" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13266,10 +13269,10 @@
         <v>407301</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D158" s="2">
         <v>407301</v>
@@ -13296,14 +13299,14 @@
         <v>0</v>
       </c>
       <c r="L158" s="22" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M158" s="22"/>
       <c r="N158" s="5">
         <v>0</v>
       </c>
       <c r="O158" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="159" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13311,7 +13314,7 @@
         <v>408101</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>131</v>
@@ -13341,7 +13344,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M159" s="22" t="s">
         <v>133</v>
@@ -13361,7 +13364,7 @@
         <v>29</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D160" s="2">
         <v>411101</v>
@@ -13385,14 +13388,14 @@
         <v>3</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L160" s="22" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M160" s="22"/>
       <c r="N160" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O160" s="5">
         <v>0</v>
@@ -13433,11 +13436,11 @@
         <v>413201</v>
       </c>
       <c r="L161" s="22" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M161" s="22"/>
       <c r="N161" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O161" s="5">
         <v>0</v>
@@ -13448,10 +13451,10 @@
         <v>412201</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D162" s="2">
         <v>412201</v>
@@ -13478,7 +13481,7 @@
         <v>414301</v>
       </c>
       <c r="L162" s="22" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M162" s="22" t="s">
         <v>148</v>
@@ -13525,11 +13528,11 @@
         <v>413101</v>
       </c>
       <c r="L163" s="22" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M163" s="22"/>
       <c r="N163" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O163" s="5">
         <v>0</v>
@@ -13540,10 +13543,10 @@
         <v>413101</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D164" s="2">
         <v>413101</v>
@@ -13570,11 +13573,11 @@
         <v>0</v>
       </c>
       <c r="L164" s="22" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M164" s="22"/>
       <c r="N164" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O164" s="5">
         <v>0</v>
@@ -13585,10 +13588,10 @@
         <v>413201</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D165" s="2">
         <v>413201</v>
@@ -13615,11 +13618,11 @@
         <v>0</v>
       </c>
       <c r="L165" s="22" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M165" s="22"/>
       <c r="N165" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O165" s="5">
         <v>0</v>
@@ -13630,10 +13633,10 @@
         <v>414101</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D166" s="2">
         <v>414101</v>
@@ -13660,7 +13663,7 @@
         <v>415101</v>
       </c>
       <c r="L166" s="22" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M166" s="22"/>
       <c r="N166" s="5">
@@ -13675,10 +13678,10 @@
         <v>414201</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D167" s="2">
         <v>414201</v>
@@ -13705,11 +13708,11 @@
         <v>414101</v>
       </c>
       <c r="L167" s="22" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M167" s="22"/>
       <c r="N167" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O167" s="5">
         <v>0</v>
@@ -13720,10 +13723,10 @@
         <v>414301</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D168" s="2">
         <v>414301</v>
@@ -13747,10 +13750,10 @@
         <v>1</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L168" s="22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M168" s="22" t="s">
         <v>176</v>
@@ -13767,10 +13770,10 @@
         <v>414401</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D169" s="2">
         <v>414401</v>
@@ -13797,14 +13800,14 @@
         <v>414501</v>
       </c>
       <c r="L169" s="22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M169" s="22"/>
       <c r="N169" s="5">
         <v>0</v>
       </c>
       <c r="O169" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="170" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13815,7 +13818,7 @@
         <v>485</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D170" s="2">
         <v>414501</v>
@@ -13842,13 +13845,13 @@
         <v>415201</v>
       </c>
       <c r="L170" s="22" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M170" s="22" t="s">
         <v>185</v>
       </c>
       <c r="N170" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O170" s="5">
         <v>0</v>
@@ -13859,10 +13862,10 @@
         <v>415101</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D171" s="2">
         <v>415101</v>
@@ -13889,7 +13892,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="22" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M171" s="22" t="s">
         <v>189</v>
@@ -13898,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="O171" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="172" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13906,10 +13909,10 @@
         <v>415201</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D172" s="2">
         <v>415201</v>
@@ -13936,7 +13939,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M172" s="22" t="s">
         <v>91</v>
@@ -13945,7 +13948,7 @@
         <v>0</v>
       </c>
       <c r="O172" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="173" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -13953,10 +13956,10 @@
         <v>416101</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D173" s="2">
         <v>416101</v>
@@ -13983,7 +13986,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="22" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M173" s="22" t="s">
         <v>193</v>
@@ -14000,10 +14003,10 @@
         <v>416201</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D174" s="2">
         <v>416201</v>
@@ -14030,14 +14033,14 @@
         <v>416101</v>
       </c>
       <c r="L174" s="22" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M174" s="22"/>
       <c r="N174" s="5">
         <v>0</v>
       </c>
       <c r="O174" s="5" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="175" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -14045,10 +14048,10 @@
         <v>416301</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D175" s="2">
         <v>416301</v>
@@ -14072,14 +14075,14 @@
         <v>1</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L175" s="22" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M175" s="22"/>
       <c r="N175" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O175" s="5">
         <v>0</v>
@@ -14093,7 +14096,7 @@
         <v>485</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D176" s="2">
         <v>416401</v>
@@ -14120,11 +14123,11 @@
         <v>416501</v>
       </c>
       <c r="L176" s="22" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M176" s="22"/>
       <c r="N176" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O176" s="5">
         <v>0</v>
@@ -14135,10 +14138,10 @@
         <v>416501</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D177" s="2">
         <v>416501</v>
@@ -14165,13 +14168,13 @@
         <v>0</v>
       </c>
       <c r="L177" s="22" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M177" s="22" t="s">
         <v>209</v>
       </c>
       <c r="N177" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O177" s="5">
         <v>0</v>
@@ -14182,10 +14185,10 @@
         <v>417101</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D178" s="2">
         <v>417101</v>
@@ -14212,14 +14215,14 @@
         <v>0</v>
       </c>
       <c r="L178" s="22" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M178" s="22"/>
       <c r="N178" s="5">
         <v>0</v>
       </c>
       <c r="O178" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="179" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
@@ -14230,7 +14233,7 @@
         <v>390</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D179" s="2">
         <v>417201</v>
@@ -14254,7 +14257,7 @@
         <v>5</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L179" s="22" t="s">
         <v>312</v>
@@ -14272,10 +14275,10 @@
         <v>417301</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D180" s="2">
         <v>417301</v>
@@ -14302,11 +14305,11 @@
         <v>0</v>
       </c>
       <c r="L180" s="22" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M180" s="22"/>
       <c r="N180" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O180" s="5">
         <v>0</v>
@@ -14317,10 +14320,10 @@
         <v>418101</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D181" s="2">
         <v>418101</v>
@@ -14347,7 +14350,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M181" s="22"/>
       <c r="N181" s="5">
@@ -14376,7 +14379,7 @@
   <sheetData>
     <row r="3" spans="3:8">
       <c r="C3" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>244</v>
@@ -14390,13 +14393,13 @@
     </row>
     <row r="5" spans="3:8">
       <c r="C5" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>244</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>

--- a/S_数据表/Talent_Template.xlsx
+++ b/S_数据表/Talent_Template.xlsx
@@ -1,52 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WYK\yongshi\S_数据表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\YongShi\S_数据表\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36D68C1-DE78-4E30-A670-BF236B22B847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="备用" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Administrator</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Administrator:
 </t>
@@ -64,7 +52,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 1</t>
@@ -82,7 +70,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>2</t>
         </r>
@@ -96,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1">
+    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -112,7 +100,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>:
 “|”</t>
@@ -132,7 +120,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">101,10   </t>
         </r>
@@ -150,7 +138,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -168,7 +156,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 //10.Hp</t>
@@ -186,7 +174,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//11.Hp</t>
         </r>
@@ -203,7 +191,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//12.</t>
         </r>
@@ -220,7 +208,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//13.</t>
         </r>
@@ -237,7 +225,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//14.</t>
         </r>
@@ -254,7 +242,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//15.</t>
         </r>
@@ -271,7 +259,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//16.</t>
         </r>
@@ -288,7 +276,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//17.</t>
         </r>
@@ -305,7 +293,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//18.</t>
         </r>
@@ -322,7 +310,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//19.</t>
         </r>
@@ -339,7 +327,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">//20 </t>
         </r>
@@ -356,7 +344,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//21.</t>
         </r>
@@ -373,7 +361,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//22.</t>
         </r>
@@ -390,7 +378,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//23.</t>
         </r>
@@ -407,7 +395,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//30.</t>
         </r>
@@ -424,7 +412,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//31.</t>
         </r>
@@ -441,7 +429,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//32.</t>
         </r>
@@ -458,7 +446,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//33.</t>
         </r>
@@ -475,7 +463,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//34.</t>
         </r>
@@ -492,7 +480,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//35.</t>
         </r>
@@ -509,7 +497,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//36.</t>
         </r>
@@ -526,7 +514,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//37.</t>
         </r>
@@ -543,7 +531,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//41.</t>
         </r>
@@ -560,7 +548,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//101</t>
         </r>
@@ -577,7 +565,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>//111</t>
         </r>
@@ -594,7 +582,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">//112:  </t>
         </r>
@@ -611,7 +599,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">//121:  </t>
         </r>
@@ -628,7 +616,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">//131:  </t>
         </r>
@@ -644,7 +632,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">   
 //132:  </t>
@@ -662,7 +650,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">//141:  </t>
         </r>
@@ -679,7 +667,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>SkillAdd</t>
         </r>
@@ -696,7 +684,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>1.</t>
         </r>
@@ -713,7 +701,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>2.</t>
         </r>
@@ -729,7 +717,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -745,7 +733,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>1</t>
         </r>
@@ -761,7 +749,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>100%</t>
         </r>
@@ -778,7 +766,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>3.</t>
         </r>
@@ -795,7 +783,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>4.</t>
         </r>
@@ -811,7 +799,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>CD
 5.</t>
@@ -829,7 +817,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>6.</t>
         </r>
@@ -845,7 +833,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>buff
 7.</t>
@@ -863,7 +851,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>8.</t>
         </r>
@@ -880,7 +868,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>9:</t>
         </r>
@@ -896,7 +884,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>(2</t>
         </r>
@@ -912,7 +900,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">  </t>
         </r>
@@ -928,7 +916,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>@</t>
         </r>
@@ -944,7 +932,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>ID)
 10.</t>
@@ -962,7 +950,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>11.</t>
         </r>
@@ -979,7 +967,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>12.</t>
         </r>
@@ -993,14 +981,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0">
+    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -1008,7 +996,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1025,7 +1013,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <charset val="134"/>
+            <family val="2"/>
           </rPr>
           <t>,</t>
         </r>
@@ -4033,9 +4021,6 @@
     <t>Magic Spirit Shield</t>
   </si>
   <si>
-    <t>406201;406401;107201</t>
-  </si>
-  <si>
     <t>新增技能:魔灵护盾 技能效果：召唤一个护盾保护自己,护盾可以承受20%最大生命的伤害,持续12秒！</t>
   </si>
   <si>
@@ -4310,19 +4295,17 @@
   </si>
   <si>
     <t>SkillAdd,60030105,5,10;SkillAdd,60030115,5,10|SkillAdd,60030105,5,15;SkillAdd,60030115,5,15|SkillAdd,60030105,5,20;SkillAdd,60030115,5,20|SkillAdd,60030105,5,25;SkillAdd,60030115,5,25|SkillAdd,60030105,5,30;SkillAdd,60030115,5,30</t>
+  </si>
+  <si>
+    <t>406201;406401;407201</t>
+    <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="42">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4371,61 +4354,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -4435,83 +4363,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4551,7 +4405,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -4601,12 +4455,12 @@
       <b/>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -4619,8 +4473,14 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="64">
+  <fills count="49">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4636,24 +4496,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4683,19 +4525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4707,19 +4537,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4731,19 +4549,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4755,19 +4561,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4779,19 +4573,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4803,204 +4585,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799920651875362"/>
+        <fgColor theme="4" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799890133365886"/>
+        <fgColor theme="5" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799951170384838"/>
+        <fgColor theme="5" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799920651875362"/>
+        <fgColor theme="5" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799890133365886"/>
+        <fgColor theme="6" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799951170384838"/>
+        <fgColor theme="6" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799920651875362"/>
+        <fgColor theme="6" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799890133365886"/>
+        <fgColor theme="7" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799951170384838"/>
+        <fgColor theme="7" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799920651875362"/>
+        <fgColor theme="7" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799890133365886"/>
+        <fgColor theme="8" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799951170384838"/>
+        <fgColor theme="8" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799920651875362"/>
+        <fgColor theme="8" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799890133365886"/>
+        <fgColor theme="9" tint="0.79989013336588644"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799951170384838"/>
+        <fgColor theme="9" tint="0.79985961485641044"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799920651875362"/>
+        <fgColor theme="9" tint="0.79992065187536243"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799890133365886"/>
+        <fgColor theme="4" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799951170384838"/>
+        <fgColor theme="4" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399914548173467"/>
+        <fgColor theme="5" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399945066682943"/>
+        <fgColor theme="5" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399914548173467"/>
+        <fgColor theme="6" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399945066682943"/>
+        <fgColor theme="6" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399914548173467"/>
+        <fgColor theme="7" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399945066682943"/>
+        <fgColor theme="7" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399914548173467"/>
+        <fgColor theme="8" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399945066682943"/>
+        <fgColor theme="8" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399914548173467"/>
+        <fgColor theme="9" tint="0.39988402966399123"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399945066682943"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399914548173467"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -5077,418 +4847,191 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="108">
+  <cellStyleXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5509,34 +5052,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="89" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5548,7 +5091,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5560,127 +5103,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="108">
+  <cellStyles count="60">
+    <cellStyle name="20% - 强调文字颜色 1 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 10 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="20% - 强调文字颜色 1 10 2 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 10" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 10 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="20% - 强调文字颜色 2 10 2 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 10" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 10 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="20% - 强调文字颜色 3 10 2 4" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 10" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 10 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="20% - 强调文字颜色 4 10 2 4" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 10" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 10 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="20% - 强调文字颜色 5 10 2 4" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 10" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 10 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="20% - 强调文字颜色 6 10 2 4" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="40% - 强调文字颜色 1 10" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="40% - 强调文字颜色 2 10" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="40% - 强调文字颜色 3 10" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="40% - 强调文字颜色 4 10" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="40% - 强调文字颜色 5 10" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="40% - 强调文字颜色 6 10" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="60% - 强调文字颜色 1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="60% - 强调文字颜色 1 2 3" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="60% - 强调文字颜色 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="60% - 强调文字颜色 2 2 3" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="60% - 强调文字颜色 3 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="60% - 强调文字颜色 3 2 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="60% - 强调文字颜色 4 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="60% - 强调文字颜色 5 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="60% - 强调文字颜色 5 2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="60% - 强调文字颜色 6 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="60% - 强调文字颜色 6 2 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="百分比 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="标题 4 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="标题 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="差 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="20% - 强调文字颜色 1 10" xfId="49"/>
-    <cellStyle name="20% - 强调文字颜色 1 10 2" xfId="50"/>
-    <cellStyle name="20% - 强调文字颜色 1 10 2 4" xfId="51"/>
-    <cellStyle name="20% - 强调文字颜色 2 10" xfId="52"/>
-    <cellStyle name="20% - 强调文字颜色 2 10 2" xfId="53"/>
-    <cellStyle name="20% - 强调文字颜色 2 10 2 4" xfId="54"/>
-    <cellStyle name="20% - 强调文字颜色 3 10" xfId="55"/>
-    <cellStyle name="20% - 强调文字颜色 3 10 2" xfId="56"/>
-    <cellStyle name="20% - 强调文字颜色 3 10 2 4" xfId="57"/>
-    <cellStyle name="20% - 强调文字颜色 4 10" xfId="58"/>
-    <cellStyle name="20% - 强调文字颜色 4 10 2" xfId="59"/>
-    <cellStyle name="20% - 强调文字颜色 4 10 2 4" xfId="60"/>
-    <cellStyle name="20% - 强调文字颜色 5 10" xfId="61"/>
-    <cellStyle name="20% - 强调文字颜色 5 10 2" xfId="62"/>
-    <cellStyle name="20% - 强调文字颜色 5 10 2 4" xfId="63"/>
-    <cellStyle name="20% - 强调文字颜色 6 10" xfId="64"/>
-    <cellStyle name="20% - 强调文字颜色 6 10 2" xfId="65"/>
-    <cellStyle name="20% - 强调文字颜色 6 10 2 4" xfId="66"/>
-    <cellStyle name="40% - 强调文字颜色 1 10" xfId="67"/>
-    <cellStyle name="40% - 强调文字颜色 2 10" xfId="68"/>
-    <cellStyle name="40% - 强调文字颜色 3 10" xfId="69"/>
-    <cellStyle name="40% - 强调文字颜色 4 10" xfId="70"/>
-    <cellStyle name="40% - 强调文字颜色 5 10" xfId="71"/>
-    <cellStyle name="40% - 强调文字颜色 6 10" xfId="72"/>
-    <cellStyle name="60% - 强调文字颜色 1 2" xfId="73"/>
-    <cellStyle name="60% - 强调文字颜色 1 2 3" xfId="74"/>
-    <cellStyle name="60% - 强调文字颜色 2 2" xfId="75"/>
-    <cellStyle name="60% - 强调文字颜色 2 2 3" xfId="76"/>
-    <cellStyle name="60% - 强调文字颜色 3 2" xfId="77"/>
-    <cellStyle name="60% - 强调文字颜色 3 2 3" xfId="78"/>
-    <cellStyle name="60% - 强调文字颜色 4 2" xfId="79"/>
-    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="80"/>
-    <cellStyle name="60% - 强调文字颜色 5 2" xfId="81"/>
-    <cellStyle name="60% - 强调文字颜色 5 2 3" xfId="82"/>
-    <cellStyle name="60% - 强调文字颜色 6 2" xfId="83"/>
-    <cellStyle name="60% - 强调文字颜色 6 2 3" xfId="84"/>
-    <cellStyle name="百分比 2" xfId="85"/>
-    <cellStyle name="标题 4 2" xfId="86"/>
-    <cellStyle name="标题 5" xfId="87"/>
-    <cellStyle name="差 2" xfId="88"/>
-    <cellStyle name="常规 10" xfId="89"/>
-    <cellStyle name="常规 10 2" xfId="90"/>
-    <cellStyle name="常规 11 2" xfId="91"/>
-    <cellStyle name="常规 3" xfId="92"/>
-    <cellStyle name="常规 6" xfId="93"/>
-    <cellStyle name="常规 8" xfId="94"/>
-    <cellStyle name="超链接 2" xfId="95"/>
-    <cellStyle name="好 2" xfId="96"/>
-    <cellStyle name="解释性文本 2" xfId="97"/>
-    <cellStyle name="警告文本 2" xfId="98"/>
-    <cellStyle name="强调文字颜色 1 2" xfId="99"/>
-    <cellStyle name="强调文字颜色 2 2" xfId="100"/>
-    <cellStyle name="强调文字颜色 3 2" xfId="101"/>
-    <cellStyle name="强调文字颜色 4 2" xfId="102"/>
-    <cellStyle name="强调文字颜色 5 2" xfId="103"/>
-    <cellStyle name="强调文字颜色 6 2" xfId="104"/>
-    <cellStyle name="适中 2" xfId="105"/>
-    <cellStyle name="注释 2" xfId="106"/>
-    <cellStyle name="注释 2 2 2 2 3" xfId="107"/>
+    <cellStyle name="常规 10" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="常规 10 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="常规 11 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="常规 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="常规 6" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="常规 8" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="超链接 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="好 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="解释性文本 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="警告文本 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="强调文字颜色 1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="强调文字颜色 2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="强调文字颜色 3 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="强调文字颜色 4 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="强调文字颜色 5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="强调文字颜色 6 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="适中 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="注释 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="注释 2 2 2 2 3" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <i val="0"/>
       </font>
       <fill>
@@ -5708,6 +5203,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5994,14 +5492,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y181"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
@@ -6016,7 +5514,7 @@
     <col min="15" max="15" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="1" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -6063,7 +5561,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="2" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -6110,7 +5608,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="3" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>8</v>
       </c>
@@ -6157,7 +5655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="4" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -6204,7 +5702,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="5" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
@@ -6251,7 +5749,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="6" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2">
         <v>101101</v>
       </c>
@@ -6298,7 +5796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="7" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2">
         <v>102101</v>
       </c>
@@ -6345,7 +5843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="8" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="2">
         <v>102201</v>
       </c>
@@ -6392,7 +5890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="9" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2">
         <v>102301</v>
       </c>
@@ -6439,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="10" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2">
         <v>103101</v>
       </c>
@@ -6486,7 +5984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="11" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2">
         <v>103201</v>
       </c>
@@ -6533,7 +6031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="12" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2">
         <v>104101</v>
       </c>
@@ -6580,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="13" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2">
         <v>104201</v>
       </c>
@@ -6627,7 +6125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="14" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2">
         <v>104301</v>
       </c>
@@ -6674,7 +6172,7 @@
         <v>60030001</v>
       </c>
     </row>
-    <row r="15" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="15" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2">
         <v>104401</v>
       </c>
@@ -6721,7 +6219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="16" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2">
         <v>104501</v>
       </c>
@@ -6768,7 +6266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="17" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2">
         <v>105101</v>
       </c>
@@ -6815,7 +6313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="18" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2">
         <v>105201</v>
       </c>
@@ -6862,7 +6360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="19" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2">
         <v>106101</v>
       </c>
@@ -6909,7 +6407,7 @@
         <v>60030006</v>
       </c>
     </row>
-    <row r="20" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="20" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2">
         <v>106201</v>
       </c>
@@ -6956,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="21" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2">
         <v>106301</v>
       </c>
@@ -7003,7 +6501,7 @@
         <v>60030002</v>
       </c>
     </row>
-    <row r="22" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="22" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="2">
         <v>106401</v>
       </c>
@@ -7050,7 +6548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="23" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="2">
         <v>106501</v>
       </c>
@@ -7097,7 +6595,7 @@
         <v>60030004</v>
       </c>
     </row>
-    <row r="24" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="24" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="2">
         <v>107101</v>
       </c>
@@ -7144,7 +6642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="25" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="2">
         <v>107201</v>
       </c>
@@ -7191,7 +6689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="26" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="2">
         <v>107301</v>
       </c>
@@ -7238,7 +6736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="27" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2">
         <v>108101</v>
       </c>
@@ -7285,7 +6783,7 @@
         <v>60030005</v>
       </c>
     </row>
-    <row r="28" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="28" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="2">
         <v>111101</v>
       </c>
@@ -7334,7 +6832,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="12"/>
     </row>
-    <row r="29" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="29" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="2">
         <v>112101</v>
       </c>
@@ -7383,7 +6881,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
     </row>
-    <row r="30" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="30" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="2">
         <v>112201</v>
       </c>
@@ -7432,7 +6930,7 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="31" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="2">
         <v>112301</v>
       </c>
@@ -7481,7 +6979,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="32" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2">
         <v>113101</v>
       </c>
@@ -7530,7 +7028,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="33" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="2">
         <v>113201</v>
       </c>
@@ -7579,7 +7077,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="34" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="2">
         <v>114101</v>
       </c>
@@ -7628,7 +7126,7 @@
       <c r="Q34" s="15"/>
       <c r="R34" s="16"/>
     </row>
-    <row r="35" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="35" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="2">
         <v>114201</v>
       </c>
@@ -7677,7 +7175,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="36" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="2">
         <v>114301</v>
       </c>
@@ -7726,7 +7224,7 @@
       <c r="Q36" s="15"/>
       <c r="R36" s="16"/>
     </row>
-    <row r="37" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="37" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="2">
         <v>114401</v>
       </c>
@@ -7775,7 +7273,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="38" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="2">
         <v>114501</v>
       </c>
@@ -7824,7 +7322,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="39" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="2">
         <v>115101</v>
       </c>
@@ -7873,7 +7371,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="40" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="2">
         <v>115201</v>
       </c>
@@ -7922,7 +7420,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="41" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="2">
         <v>116101</v>
       </c>
@@ -7971,7 +7469,7 @@
       <c r="Q41" s="17"/>
       <c r="R41" s="18"/>
     </row>
-    <row r="42" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="42" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="2">
         <v>116201</v>
       </c>
@@ -8018,7 +7516,7 @@
       <c r="Q42" s="11"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="43" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="2">
         <v>116301</v>
       </c>
@@ -8067,7 +7565,7 @@
       <c r="Q43" s="15"/>
       <c r="R43" s="16"/>
     </row>
-    <row r="44" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="44" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="2">
         <v>116401</v>
       </c>
@@ -8114,7 +7612,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="45" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="2">
         <v>116501</v>
       </c>
@@ -8163,7 +7661,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="18"/>
     </row>
-    <row r="46" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="46" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="2">
         <v>117101</v>
       </c>
@@ -8212,7 +7710,7 @@
       <c r="Q46" s="20"/>
       <c r="R46" s="12"/>
     </row>
-    <row r="47" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="47" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="2">
         <v>117201</v>
       </c>
@@ -8261,7 +7759,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
+    <row r="48" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="2">
         <v>117301</v>
       </c>
@@ -8310,7 +7808,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="49" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="2">
         <v>118101</v>
       </c>
@@ -8359,7 +7857,7 @@
       <c r="Q49" s="15"/>
       <c r="R49" s="16"/>
     </row>
-    <row r="50" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="50" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="2">
         <v>201101</v>
       </c>
@@ -8406,7 +7904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="51" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="2">
         <v>202101</v>
       </c>
@@ -8450,7 +7948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="52" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="2">
         <v>202201</v>
       </c>
@@ -8494,7 +7992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="53" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="2">
         <v>202301</v>
       </c>
@@ -8541,7 +8039,7 @@
         <v>90001033</v>
       </c>
     </row>
-    <row r="54" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="54" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="2">
         <v>203101</v>
       </c>
@@ -8597,7 +8095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="55" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="2">
         <v>203201</v>
       </c>
@@ -8641,7 +8139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="56" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="2">
         <v>204101</v>
       </c>
@@ -8683,7 +8181,7 @@
         <v>60030109</v>
       </c>
     </row>
-    <row r="57" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="57" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="2">
         <v>204201</v>
       </c>
@@ -8726,7 +8224,7 @@
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="58" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="2">
         <v>204301</v>
       </c>
@@ -8768,7 +8266,7 @@
         <v>60030101</v>
       </c>
     </row>
-    <row r="59" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="59" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="2">
         <v>204401</v>
       </c>
@@ -8821,7 +8319,7 @@
         <v>205101</v>
       </c>
     </row>
-    <row r="60" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="60" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="2">
         <v>204501</v>
       </c>
@@ -8865,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="61" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="2">
         <v>205101</v>
       </c>
@@ -8910,7 +8408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="62" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="2">
         <v>205201</v>
       </c>
@@ -8955,7 +8453,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="63" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="63" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="2">
         <v>206101</v>
       </c>
@@ -8997,7 +8495,7 @@
         <v>60030110</v>
       </c>
     </row>
-    <row r="64" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
+    <row r="64" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="2">
         <v>206201</v>
       </c>
@@ -9041,7 +8539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="65" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="2">
         <v>206301</v>
       </c>
@@ -9085,7 +8583,7 @@
         <v>60030102</v>
       </c>
     </row>
-    <row r="66" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="2">
         <v>206401</v>
       </c>
@@ -9129,7 +8627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="67" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="2">
         <v>206501</v>
       </c>
@@ -9171,7 +8669,7 @@
         <v>60030111</v>
       </c>
     </row>
-    <row r="68" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="68" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="2">
         <v>207101</v>
       </c>
@@ -9215,7 +8713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="69" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="2">
         <v>207201</v>
       </c>
@@ -9259,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="70" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="2">
         <v>207301</v>
       </c>
@@ -9303,7 +8801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="71" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="2">
         <v>208101</v>
       </c>
@@ -9347,7 +8845,7 @@
         <v>60030104</v>
       </c>
     </row>
-    <row r="72" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="72" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="2">
         <v>211101</v>
       </c>
@@ -9394,7 +8892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="73" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="2">
         <v>212101</v>
       </c>
@@ -9437,7 +8935,7 @@
       </c>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="74" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="2">
         <v>212201</v>
       </c>
@@ -9482,7 +8980,7 @@
         <v>60030105</v>
       </c>
     </row>
-    <row r="75" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="75" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="2">
         <v>212301</v>
       </c>
@@ -9527,7 +9025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="76" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="2">
         <v>213101</v>
       </c>
@@ -9574,7 +9072,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="77" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="77" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="2">
         <v>213201</v>
       </c>
@@ -9618,7 +9116,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="78" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="78" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="2">
         <v>214101</v>
       </c>
@@ -9663,7 +9161,7 @@
         <v>60030114</v>
       </c>
     </row>
-    <row r="79" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="79" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="2">
         <v>214201</v>
       </c>
@@ -9710,7 +9208,7 @@
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
     </row>
-    <row r="80" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="80" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="2">
         <v>214301</v>
       </c>
@@ -9757,7 +9255,7 @@
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
     </row>
-    <row r="81" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="81" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="2">
         <v>214401</v>
       </c>
@@ -9804,7 +9302,7 @@
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
     </row>
-    <row r="82" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="82" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="2">
         <v>214501</v>
       </c>
@@ -9851,7 +9349,7 @@
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
     </row>
-    <row r="83" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="83" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="2">
         <v>215101</v>
       </c>
@@ -9900,7 +9398,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="84" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="84" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="2">
         <v>215201</v>
       </c>
@@ -9949,7 +9447,7 @@
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
     </row>
-    <row r="85" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="85" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="2">
         <v>216101</v>
       </c>
@@ -9991,7 +9489,7 @@
         <v>60030110</v>
       </c>
     </row>
-    <row r="86" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="86" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="2">
         <v>216201</v>
       </c>
@@ -10038,7 +9536,7 @@
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
     </row>
-    <row r="87" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="87" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="2">
         <v>216301</v>
       </c>
@@ -10085,7 +9583,7 @@
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
     </row>
-    <row r="88" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="88" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="2">
         <v>216401</v>
       </c>
@@ -10132,7 +9630,7 @@
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
     </row>
-    <row r="89" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="89" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="2">
         <v>216501</v>
       </c>
@@ -10179,7 +9677,7 @@
       <c r="P89" s="2"/>
       <c r="Q89" s="2"/>
     </row>
-    <row r="90" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="90" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="2">
         <v>217101</v>
       </c>
@@ -10224,7 +9722,7 @@
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
     </row>
-    <row r="91" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="91" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="2">
         <v>217201</v>
       </c>
@@ -10271,7 +9769,7 @@
       <c r="P91" s="2"/>
       <c r="Q91" s="2"/>
     </row>
-    <row r="92" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="92" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="2">
         <v>217301</v>
       </c>
@@ -10322,7 +9820,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="93" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="93" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="2">
         <v>218101</v>
       </c>
@@ -10369,7 +9867,7 @@
       <c r="P93" s="2"/>
       <c r="Q93" s="2"/>
     </row>
-    <row r="94" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="94" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="2">
         <v>301101</v>
       </c>
@@ -10416,7 +9914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="95" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="2">
         <v>302101</v>
       </c>
@@ -10461,7 +9959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
+    <row r="96" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="2">
         <v>302201</v>
       </c>
@@ -10506,7 +10004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="97" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="2">
         <v>302301</v>
       </c>
@@ -10551,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="98" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="2">
         <v>303101</v>
       </c>
@@ -10597,7 +10095,7 @@
       <c r="U98" s="5"/>
       <c r="V98" s="5"/>
     </row>
-    <row r="99" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="99" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="2">
         <v>303201</v>
       </c>
@@ -10639,7 +10137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="100" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="2">
         <v>304101</v>
       </c>
@@ -10682,7 +10180,7 @@
         <v>60032001</v>
       </c>
     </row>
-    <row r="101" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="101" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="2">
         <v>304201</v>
       </c>
@@ -10727,7 +10225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="102" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="2">
         <v>304301</v>
       </c>
@@ -10770,7 +10268,7 @@
         <v>60032002</v>
       </c>
     </row>
-    <row r="103" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="103" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="2">
         <v>304401</v>
       </c>
@@ -10813,7 +10311,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="104" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="104" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="2">
         <v>304501</v>
       </c>
@@ -10858,7 +10356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="105" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="2">
         <v>305101</v>
       </c>
@@ -10903,7 +10401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="106" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="2">
         <v>305201</v>
       </c>
@@ -10948,7 +10446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="107" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="2">
         <v>306101</v>
       </c>
@@ -10991,7 +10489,7 @@
       </c>
       <c r="O107" s="5"/>
     </row>
-    <row r="108" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="108" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="2">
         <v>306201</v>
       </c>
@@ -11036,7 +10534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="109" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="2">
         <v>306301</v>
       </c>
@@ -11081,7 +10579,7 @@
         <v>60032021</v>
       </c>
     </row>
-    <row r="110" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="110" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="2">
         <v>306401</v>
       </c>
@@ -11126,7 +10624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="111" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="2">
         <v>306501</v>
       </c>
@@ -11171,7 +10669,7 @@
         <v>60032005</v>
       </c>
     </row>
-    <row r="112" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
+    <row r="112" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="2">
         <v>307101</v>
       </c>
@@ -11216,7 +10714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="113" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="2">
         <v>307201</v>
       </c>
@@ -11263,7 +10761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="114" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="2">
         <v>307301</v>
       </c>
@@ -11306,7 +10804,7 @@
       </c>
       <c r="O114" s="5"/>
     </row>
-    <row r="115" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="115" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="5">
         <v>308101</v>
       </c>
@@ -11351,7 +10849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="116" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="2">
         <v>311101</v>
       </c>
@@ -11396,7 +10894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="117" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="2">
         <v>312101</v>
       </c>
@@ -11441,7 +10939,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="118" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="118" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="2">
         <v>312201</v>
       </c>
@@ -11486,7 +10984,7 @@
         <v>60032101</v>
       </c>
     </row>
-    <row r="119" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="119" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="2">
         <v>312301</v>
       </c>
@@ -11531,7 +11029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="120" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="2">
         <v>313101</v>
       </c>
@@ -11576,7 +11074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="121" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="2">
         <v>313201</v>
       </c>
@@ -11621,7 +11119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="122" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="2">
         <v>314101</v>
       </c>
@@ -11666,7 +11164,7 @@
         <v>60032141</v>
       </c>
     </row>
-    <row r="123" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="123" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="2">
         <v>314201</v>
       </c>
@@ -11711,7 +11209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="124" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2">
         <v>314301</v>
       </c>
@@ -11756,7 +11254,7 @@
         <v>60032131</v>
       </c>
     </row>
-    <row r="125" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="125" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="2">
         <v>314401</v>
       </c>
@@ -11801,7 +11299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="126" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="2">
         <v>314501</v>
       </c>
@@ -11846,7 +11344,7 @@
         <v>60032151</v>
       </c>
     </row>
-    <row r="127" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="127" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="2">
         <v>315101</v>
       </c>
@@ -11891,7 +11389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
+    <row r="128" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="2">
         <v>315201</v>
       </c>
@@ -11937,7 +11435,7 @@
       </c>
       <c r="P128" s="6"/>
     </row>
-    <row r="129" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="129" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="2">
         <v>316101</v>
       </c>
@@ -11982,7 +11480,7 @@
         <v>60032161</v>
       </c>
     </row>
-    <row r="130" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="130" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="2">
         <v>316201</v>
       </c>
@@ -12025,7 +11523,7 @@
       </c>
       <c r="O130" s="5"/>
     </row>
-    <row r="131" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="131" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2">
         <v>316301</v>
       </c>
@@ -12070,7 +11568,7 @@
         <v>60032162</v>
       </c>
     </row>
-    <row r="132" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="132" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="2">
         <v>316401</v>
       </c>
@@ -12115,7 +11613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="133" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="2">
         <v>316501</v>
       </c>
@@ -12158,7 +11656,7 @@
         <v>60032004</v>
       </c>
     </row>
-    <row r="134" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="134" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="2">
         <v>317101</v>
       </c>
@@ -12205,7 +11703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="135" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="2">
         <v>317201</v>
       </c>
@@ -12250,7 +11748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="136" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="2">
         <v>317301</v>
       </c>
@@ -12295,7 +11793,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="137" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="137" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="2">
         <v>318101</v>
       </c>
@@ -12340,7 +11838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="138" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="2">
         <v>401101</v>
       </c>
@@ -12385,7 +11883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="139" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="2">
         <v>402101</v>
       </c>
@@ -12430,7 +11928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="140" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="2">
         <v>402201</v>
       </c>
@@ -12475,7 +11973,7 @@
         <v>60040058</v>
       </c>
     </row>
-    <row r="141" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="141" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="2">
         <v>402301</v>
       </c>
@@ -12520,7 +12018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="142" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="2">
         <v>403101</v>
       </c>
@@ -12567,7 +12065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="143" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="2">
         <v>403201</v>
       </c>
@@ -12614,7 +12112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="144" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="2">
         <v>404101</v>
       </c>
@@ -12659,7 +12157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="145" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="2">
         <v>404201</v>
       </c>
@@ -12706,7 +12204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="146" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="2">
         <v>404301</v>
       </c>
@@ -12753,7 +12251,7 @@
         <v>60040001</v>
       </c>
     </row>
-    <row r="147" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="147" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="2">
         <v>404401</v>
       </c>
@@ -12800,7 +12298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="148" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="2">
         <v>404501</v>
       </c>
@@ -12847,7 +12345,7 @@
         <v>60040002</v>
       </c>
     </row>
-    <row r="149" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="149" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="2">
         <v>405101</v>
       </c>
@@ -12894,7 +12392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="150" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="2">
         <v>405201</v>
       </c>
@@ -12939,7 +12437,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="151" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="151" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="2">
         <v>406101</v>
       </c>
@@ -12986,7 +12484,7 @@
         <v>60040060</v>
       </c>
     </row>
-    <row r="152" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="152" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="2">
         <v>406201</v>
       </c>
@@ -13031,7 +12529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="153" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="2">
         <v>406301</v>
       </c>
@@ -13057,16 +12555,16 @@
         <v>1</v>
       </c>
       <c r="I153" s="2">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J153" s="2">
         <v>1</v>
       </c>
       <c r="K153" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="L153" s="22" t="s">
         <v>502</v>
-      </c>
-      <c r="L153" s="22" t="s">
-        <v>503</v>
       </c>
       <c r="M153" s="22" t="s">
         <v>105</v>
@@ -13078,15 +12576,15 @@
         <v>60040003</v>
       </c>
     </row>
-    <row r="154" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="154" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="2">
         <v>406401</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="D154" s="2">
         <v>406401</v>
@@ -13113,24 +12611,24 @@
         <v>406501</v>
       </c>
       <c r="L154" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="M154" s="22" t="s">
         <v>86</v>
       </c>
       <c r="N154" s="5" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="O154" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="155" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="155" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="2">
         <v>406501</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>112</v>
@@ -13160,7 +12658,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="22" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="M155" s="22" t="s">
         <v>112</v>
@@ -13172,15 +12670,15 @@
         <v>60040004</v>
       </c>
     </row>
-    <row r="156" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="156" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="2">
         <v>407101</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="D156" s="2">
         <v>407101</v>
@@ -13207,22 +12705,22 @@
         <v>0</v>
       </c>
       <c r="L156" s="22" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M156" s="22"/>
       <c r="N156" s="5">
         <v>0</v>
       </c>
       <c r="O156" s="5" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="157" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="157" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="2">
         <v>407201</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>120</v>
@@ -13249,10 +12747,10 @@
         <v>5</v>
       </c>
       <c r="K157" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="L157" s="22" t="s">
         <v>515</v>
-      </c>
-      <c r="L157" s="22" t="s">
-        <v>516</v>
       </c>
       <c r="M157" s="22" t="s">
         <v>123</v>
@@ -13261,18 +12759,18 @@
         <v>0</v>
       </c>
       <c r="O157" s="5" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="158" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="2">
         <v>407301</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="D158" s="2">
         <v>407301</v>
@@ -13299,22 +12797,22 @@
         <v>0</v>
       </c>
       <c r="L158" s="22" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="M158" s="22"/>
       <c r="N158" s="5">
         <v>0</v>
       </c>
       <c r="O158" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="159" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="2">
         <v>408101</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>131</v>
@@ -13344,7 +12842,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="22" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="M159" s="22" t="s">
         <v>133</v>
@@ -13356,7 +12854,7 @@
         <v>60040059</v>
       </c>
     </row>
-    <row r="160" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="160" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="2">
         <v>411101</v>
       </c>
@@ -13364,7 +12862,7 @@
         <v>29</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D160" s="2">
         <v>411101</v>
@@ -13388,20 +12886,20 @@
         <v>3</v>
       </c>
       <c r="K160" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="L160" s="22" t="s">
         <v>525</v>
-      </c>
-      <c r="L160" s="22" t="s">
-        <v>526</v>
       </c>
       <c r="M160" s="22"/>
       <c r="N160" s="5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="O160" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="161" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="161" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="2">
         <v>412101</v>
       </c>
@@ -13436,25 +12934,25 @@
         <v>413201</v>
       </c>
       <c r="L161" s="22" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="M161" s="22"/>
       <c r="N161" s="5" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O161" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="162" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="162" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="2">
         <v>412201</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D162" s="2">
         <v>412201</v>
@@ -13481,7 +12979,7 @@
         <v>414301</v>
       </c>
       <c r="L162" s="22" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="M162" s="22" t="s">
         <v>148</v>
@@ -13493,7 +12991,7 @@
         <v>60040011</v>
       </c>
     </row>
-    <row r="163" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="163" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="2">
         <v>412301</v>
       </c>
@@ -13528,25 +13026,25 @@
         <v>413101</v>
       </c>
       <c r="L163" s="22" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M163" s="22"/>
       <c r="N163" s="5" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="O163" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="164" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="164" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="2">
         <v>413101</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C164" s="2" t="s">
         <v>535</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="D164" s="2">
         <v>413101</v>
@@ -13573,25 +13071,25 @@
         <v>0</v>
       </c>
       <c r="L164" s="22" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M164" s="22"/>
       <c r="N164" s="5" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="O164" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="165" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="165" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="2">
         <v>413201</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C165" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="D165" s="2">
         <v>413201</v>
@@ -13618,25 +13116,25 @@
         <v>0</v>
       </c>
       <c r="L165" s="22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M165" s="22"/>
       <c r="N165" s="5" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="O165" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="166" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="166" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="2">
         <v>414101</v>
       </c>
       <c r="B166" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C166" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="D166" s="2">
         <v>414101</v>
@@ -13663,7 +13161,7 @@
         <v>415101</v>
       </c>
       <c r="L166" s="22" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M166" s="22"/>
       <c r="N166" s="5">
@@ -13673,15 +13171,15 @@
         <v>60040012</v>
       </c>
     </row>
-    <row r="167" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="167" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="2">
         <v>414201</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C167" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="D167" s="2">
         <v>414201</v>
@@ -13708,25 +13206,25 @@
         <v>414101</v>
       </c>
       <c r="L167" s="22" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M167" s="22"/>
       <c r="N167" s="5" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="O167" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="168" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="168" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="2">
         <v>414301</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C168" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="D168" s="2">
         <v>414301</v>
@@ -13750,10 +13248,10 @@
         <v>1</v>
       </c>
       <c r="K168" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="L168" s="22" t="s">
         <v>552</v>
-      </c>
-      <c r="L168" s="22" t="s">
-        <v>553</v>
       </c>
       <c r="M168" s="22" t="s">
         <v>176</v>
@@ -13765,15 +13263,15 @@
         <v>60040013</v>
       </c>
     </row>
-    <row r="169" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="169" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="2">
         <v>414401</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D169" s="2">
         <v>414401</v>
@@ -13800,17 +13298,17 @@
         <v>414501</v>
       </c>
       <c r="L169" s="22" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="M169" s="22"/>
       <c r="N169" s="5">
         <v>0</v>
       </c>
       <c r="O169" s="5" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="170" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="2">
         <v>414501</v>
       </c>
@@ -13818,7 +13316,7 @@
         <v>485</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D170" s="2">
         <v>414501</v>
@@ -13845,27 +13343,27 @@
         <v>415201</v>
       </c>
       <c r="L170" s="22" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="M170" s="22" t="s">
         <v>185</v>
       </c>
       <c r="N170" s="5" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="O170" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="171" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="171" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A171" s="2">
         <v>415101</v>
       </c>
       <c r="B171" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C171" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D171" s="2">
         <v>415101</v>
@@ -13892,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="22" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="M171" s="22" t="s">
         <v>189</v>
@@ -13901,18 +13399,18 @@
         <v>0</v>
       </c>
       <c r="O171" s="5" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="172" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A172" s="2">
         <v>415201</v>
       </c>
       <c r="B172" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="C172" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>531</v>
       </c>
       <c r="D172" s="2">
         <v>415201</v>
@@ -13939,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="22" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="M172" s="22" t="s">
         <v>91</v>
@@ -13948,18 +13446,18 @@
         <v>0</v>
       </c>
       <c r="O172" s="5" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="173" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="2">
         <v>416101</v>
       </c>
       <c r="B173" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C173" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="D173" s="2">
         <v>416101</v>
@@ -13986,7 +13484,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="22" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="M173" s="22" t="s">
         <v>193</v>
@@ -13998,15 +13496,15 @@
         <v>60040034</v>
       </c>
     </row>
-    <row r="174" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="174" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="2">
         <v>416201</v>
       </c>
       <c r="B174" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C174" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="D174" s="2">
         <v>416201</v>
@@ -14033,25 +13531,25 @@
         <v>416101</v>
       </c>
       <c r="L174" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="M174" s="22"/>
       <c r="N174" s="5">
         <v>0</v>
       </c>
       <c r="O174" s="5" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="175" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="2">
         <v>416301</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="C175" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="D175" s="2">
         <v>416301</v>
@@ -14075,20 +13573,20 @@
         <v>1</v>
       </c>
       <c r="K175" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="L175" s="22" t="s">
         <v>570</v>
-      </c>
-      <c r="L175" s="22" t="s">
-        <v>571</v>
       </c>
       <c r="M175" s="22"/>
       <c r="N175" s="5" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="O175" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="176" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="176" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="2">
         <v>416401</v>
       </c>
@@ -14096,7 +13594,7 @@
         <v>485</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D176" s="2">
         <v>416401</v>
@@ -14123,25 +13621,25 @@
         <v>416501</v>
       </c>
       <c r="L176" s="22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="M176" s="22"/>
       <c r="N176" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O176" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="177" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="177" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="2">
         <v>416501</v>
       </c>
       <c r="B177" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C177" s="2" t="s">
         <v>575</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>576</v>
       </c>
       <c r="D177" s="2">
         <v>416501</v>
@@ -14168,27 +13666,27 @@
         <v>0</v>
       </c>
       <c r="L177" s="22" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M177" s="22" t="s">
         <v>209</v>
       </c>
       <c r="N177" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="O177" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="178" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="178" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A178" s="2">
         <v>417101</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="D178" s="2">
         <v>417101</v>
@@ -14215,17 +13713,17 @@
         <v>0</v>
       </c>
       <c r="L178" s="22" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="M178" s="22"/>
       <c r="N178" s="5">
         <v>0</v>
       </c>
       <c r="O178" s="5" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="179" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A179" s="2">
         <v>417201</v>
       </c>
@@ -14233,7 +13731,7 @@
         <v>390</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D179" s="2">
         <v>417201</v>
@@ -14257,7 +13755,7 @@
         <v>5</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="L179" s="22" t="s">
         <v>312</v>
@@ -14270,15 +13768,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="180" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A180" s="2">
         <v>417301</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="D180" s="2">
         <v>417301</v>
@@ -14305,25 +13803,25 @@
         <v>0</v>
       </c>
       <c r="L180" s="22" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M180" s="22"/>
       <c r="N180" s="5" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="O180" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="181" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
+    <row r="181" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A181" s="2">
         <v>418101</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="D181" s="2">
         <v>418101</v>
@@ -14350,7 +13848,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="22" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M181" s="22"/>
       <c r="N181" s="5">
@@ -14361,25 +13859,24 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <phoneticPr fontId="25" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="C3:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="137.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C3" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>244</v>
@@ -14391,15 +13888,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:8">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C5" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>244</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -14408,7 +13905,7 @@
       <c r="H5" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/S_数据表/Talent_Template.xlsx
+++ b/S_数据表/Talent_Template.xlsx
@@ -1,40 +1,52 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\YongShi\S_数据表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WYK\yongshi\S_数据表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36D68C1-DE78-4E30-A670-BF236B22B847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="备用" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Administrator</author>
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">Administrator:
 </t>
@@ -52,7 +64,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 1</t>
@@ -70,7 +82,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2</t>
         </r>
@@ -84,7 +96,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="N1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -100,7 +112,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>:
 “|”</t>
@@ -120,7 +132,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">101,10   </t>
         </r>
@@ -138,7 +150,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -156,7 +168,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 //10.Hp</t>
@@ -174,7 +186,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//11.Hp</t>
         </r>
@@ -191,7 +203,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//12.</t>
         </r>
@@ -208,7 +220,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//13.</t>
         </r>
@@ -225,7 +237,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//14.</t>
         </r>
@@ -242,7 +254,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//15.</t>
         </r>
@@ -259,7 +271,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//16.</t>
         </r>
@@ -276,7 +288,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//17.</t>
         </r>
@@ -293,7 +305,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//18.</t>
         </r>
@@ -310,7 +322,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//19.</t>
         </r>
@@ -327,7 +339,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">//20 </t>
         </r>
@@ -344,7 +356,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//21.</t>
         </r>
@@ -361,7 +373,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//22.</t>
         </r>
@@ -378,7 +390,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//23.</t>
         </r>
@@ -395,7 +407,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//30.</t>
         </r>
@@ -412,7 +424,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//31.</t>
         </r>
@@ -429,7 +441,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//32.</t>
         </r>
@@ -446,7 +458,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//33.</t>
         </r>
@@ -463,7 +475,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//34.</t>
         </r>
@@ -480,7 +492,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//35.</t>
         </r>
@@ -497,7 +509,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//36.</t>
         </r>
@@ -514,7 +526,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//37.</t>
         </r>
@@ -531,7 +543,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//41.</t>
         </r>
@@ -548,7 +560,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//101</t>
         </r>
@@ -565,7 +577,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>//111</t>
         </r>
@@ -582,7 +594,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">//112:  </t>
         </r>
@@ -599,7 +611,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">//121:  </t>
         </r>
@@ -616,7 +628,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">//131:  </t>
         </r>
@@ -632,7 +644,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">   
 //132:  </t>
@@ -650,7 +662,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">//141:  </t>
         </r>
@@ -667,7 +679,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>SkillAdd</t>
         </r>
@@ -684,7 +696,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1.</t>
         </r>
@@ -701,7 +713,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>2.</t>
         </r>
@@ -717,7 +729,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -733,7 +745,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>1</t>
         </r>
@@ -749,7 +761,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>100%</t>
         </r>
@@ -766,7 +778,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>3.</t>
         </r>
@@ -783,7 +795,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>4.</t>
         </r>
@@ -799,7 +811,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>CD
 5.</t>
@@ -817,7 +829,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>6.</t>
         </r>
@@ -833,7 +845,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>buff
 7.</t>
@@ -851,7 +863,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>8.</t>
         </r>
@@ -868,7 +880,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>9:</t>
         </r>
@@ -884,7 +896,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>(2</t>
         </r>
@@ -900,7 +912,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">  </t>
         </r>
@@ -916,7 +928,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>@</t>
         </r>
@@ -932,7 +944,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>ID)
 10.</t>
@@ -950,7 +962,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>11.</t>
         </r>
@@ -967,7 +979,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>12.</t>
         </r>
@@ -981,14 +993,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
         </r>
@@ -996,7 +1008,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
 </t>
@@ -1013,7 +1025,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="134"/>
           </rPr>
           <t>,</t>
         </r>
@@ -4021,6 +4033,9 @@
     <t>Magic Spirit Shield</t>
   </si>
   <si>
+    <t>406201;406401;407201</t>
+  </si>
+  <si>
     <t>新增技能:魔灵护盾 技能效果：召唤一个护盾保护自己,护盾可以承受20%最大生命的伤害,持续12秒！</t>
   </si>
   <si>
@@ -4234,7 +4249,7 @@
     <t>护体之球技能伤害提升5%;护体之球技能伤害提升10%;护体之球技能伤害提升15%;护体之球技能伤害提升20%;护体之球技能伤害提升25%</t>
   </si>
   <si>
-    <t>SkillAdd,60013021,10,0.05;SkillAdd,60013022,10,0.05;SkillAdd,60013023,10,0.05;SkillAdd,60013024,10,0.05;SkillAdd,660013025,10,0.05|SkillAdd,60013021,10,0.1;SkillAdd,60013022,10,0.1;SkillAdd,60013023,10,0.1;SkillAdd,60013024,10,0.1;SkillAdd,660013025,10,0.1|SkillAdd,60013021,10,0.15;SkillAdd,60013022,10,0.15;SkillAdd,60013023,10,0.15;SkillAdd,60013024,10,0.15;SkillAdd,660013025,10,0.15|SkillAdd,60013021,10,0.2;SkillAdd,60013022,10,0.2;SkillAdd,60013023,10,0.2;SkillAdd,60013024,10,0.2;SkillAdd,660013025,10,0.2|SkillAdd,60013021,10,0.25;SkillAdd,60013022,10,0.25;SkillAdd,60013023,10,0.25;SkillAdd,60013024,10,0.25;SkillAdd,660013025,10,0.25</t>
+    <t>SkillAdd,60013031,10,0.05;SkillAdd,60013032,10,0.05;SkillAdd,60013033,10,0.05;SkillAdd,60013034,10,0.05;SkillAdd,660013035,10,0.05|SkillAdd,60013031,10,0.1;SkillAdd,60013032,10,0.1;SkillAdd,60013033,10,0.1;SkillAdd,60013034,10,0.1;SkillAdd,660013035,10,0.1|SkillAdd,60013031,10,0.15;SkillAdd,60013032,10,0.15;SkillAdd,60013033,10,0.15;SkillAdd,60013034,10,0.15;SkillAdd,660013035,10,0.15|SkillAdd,60013031,10,0.2;SkillAdd,60013032,10,0.2;SkillAdd,60013033,10,0.2;SkillAdd,60013034,10,0.2;SkillAdd,660013035,10,0.2|SkillAdd,60013031,10,0.25;SkillAdd,60013032,10,0.25;SkillAdd,60013033,10,0.25;SkillAdd,60013034,10,0.25;SkillAdd,660013035,10,0.25</t>
   </si>
   <si>
     <t>护体感电</t>
@@ -4295,17 +4310,19 @@
   </si>
   <si>
     <t>SkillAdd,60030105,5,10;SkillAdd,60030115,5,10|SkillAdd,60030105,5,15;SkillAdd,60030115,5,15|SkillAdd,60030105,5,20;SkillAdd,60030115,5,20|SkillAdd,60030105,5,25;SkillAdd,60030115,5,25|SkillAdd,60030105,5,30;SkillAdd,60030115,5,30</t>
-  </si>
-  <si>
-    <t>406201;406401;407201</t>
-    <phoneticPr fontId="25" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="26" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4354,6 +4371,61 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -4363,9 +4435,83 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4405,7 +4551,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -4454,18 +4600,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4473,14 +4619,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="49">
+  <fills count="80">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4496,6 +4636,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4525,7 +4683,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4537,7 +4707,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4549,7 +4731,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4561,7 +4755,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4573,7 +4779,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4585,192 +4803,300 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79989013336588644"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79985961485641044"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79992065187536243"/>
+        <fgColor theme="4" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79989013336588644"/>
+        <fgColor theme="4" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79985961485641044"/>
+        <fgColor theme="4" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79992065187536243"/>
+        <fgColor theme="5" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79989013336588644"/>
+        <fgColor theme="5" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79985961485641044"/>
+        <fgColor theme="5" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79992065187536243"/>
+        <fgColor theme="6" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79989013336588644"/>
+        <fgColor theme="6" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79985961485641044"/>
+        <fgColor theme="6" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79992065187536243"/>
+        <fgColor theme="7" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79989013336588644"/>
+        <fgColor theme="7" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79985961485641044"/>
+        <fgColor theme="7" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79992065187536243"/>
+        <fgColor theme="8" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79989013336588644"/>
+        <fgColor theme="8" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79985961485641044"/>
+        <fgColor theme="8" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79992065187536243"/>
+        <fgColor theme="9" tint="0.799890133365886"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39988402966399123"/>
+        <fgColor theme="9" tint="0.79985961485641"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39991454817346722"/>
+        <fgColor theme="9" tint="0.799920651875362"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39988402966399123"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39991454817346722"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39988402966399123"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39991454817346722"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39988402966399123"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39991454817346722"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39988402966399123"/>
+        <fgColor theme="4" tint="0.399884029663991"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39991454817346722"/>
+        <fgColor theme="4" tint="0.399914548173467"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39988402966399123"/>
+        <fgColor theme="5" tint="0.399884029663991"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39991454817346722"/>
+        <fgColor theme="5" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399884029663991"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399884029663991"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399884029663991"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399884029663991"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399914548173467"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -4847,191 +5173,418 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="60">
+  <cellStyleXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="54" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="55" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="56" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="57" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="58" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="59" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="60" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="61" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="62" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="63" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="64" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="65" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="66" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="67" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="68" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="69" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="70" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="71" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="72" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="73" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="74" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="75" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="76" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="77" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="78" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="79" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="79" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5052,34 +5605,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="46" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="94" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="41" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="89" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5091,7 +5644,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5103,79 +5656,127 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="45" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="93" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="60">
-    <cellStyle name="20% - 强调文字颜色 1 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 10 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
-    <cellStyle name="20% - 强调文字颜色 1 10 2 4" xfId="3" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 10" xfId="4" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 10 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
-    <cellStyle name="20% - 强调文字颜色 2 10 2 4" xfId="6" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 10" xfId="7" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 10 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
-    <cellStyle name="20% - 强调文字颜色 3 10 2 4" xfId="9" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 10" xfId="10" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 10 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
-    <cellStyle name="20% - 强调文字颜色 4 10 2 4" xfId="12" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 10" xfId="13" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 10 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
-    <cellStyle name="20% - 强调文字颜色 5 10 2 4" xfId="15" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 10" xfId="16" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 10 2" xfId="17" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
-    <cellStyle name="20% - 强调文字颜色 6 10 2 4" xfId="18" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
-    <cellStyle name="40% - 强调文字颜色 1 10" xfId="19" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
-    <cellStyle name="40% - 强调文字颜色 2 10" xfId="20" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
-    <cellStyle name="40% - 强调文字颜色 3 10" xfId="21" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
-    <cellStyle name="40% - 强调文字颜色 4 10" xfId="22" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
-    <cellStyle name="40% - 强调文字颜色 5 10" xfId="23" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
-    <cellStyle name="40% - 强调文字颜色 6 10" xfId="24" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
-    <cellStyle name="60% - 强调文字颜色 1 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
-    <cellStyle name="60% - 强调文字颜色 1 2 3" xfId="26" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
-    <cellStyle name="60% - 强调文字颜色 2 2" xfId="27" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
-    <cellStyle name="60% - 强调文字颜色 2 2 3" xfId="28" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
-    <cellStyle name="60% - 强调文字颜色 3 2" xfId="29" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
-    <cellStyle name="60% - 强调文字颜色 3 2 3" xfId="30" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
-    <cellStyle name="60% - 强调文字颜色 4 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
-    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="32" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
-    <cellStyle name="60% - 强调文字颜色 5 2" xfId="33" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
-    <cellStyle name="60% - 强调文字颜色 5 2 3" xfId="34" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
-    <cellStyle name="60% - 强调文字颜色 6 2" xfId="35" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
-    <cellStyle name="60% - 强调文字颜色 6 2 3" xfId="36" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
-    <cellStyle name="百分比 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
-    <cellStyle name="标题 4 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
-    <cellStyle name="标题 5" xfId="39" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
-    <cellStyle name="差 2" xfId="40" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+  <cellStyles count="108">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 10" xfId="41" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
-    <cellStyle name="常规 10 2" xfId="42" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
-    <cellStyle name="常规 11 2" xfId="43" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
-    <cellStyle name="常规 3" xfId="44" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
-    <cellStyle name="常规 6" xfId="45" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
-    <cellStyle name="常规 8" xfId="46" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
-    <cellStyle name="超链接 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
-    <cellStyle name="好 2" xfId="48" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
-    <cellStyle name="解释性文本 2" xfId="49" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
-    <cellStyle name="警告文本 2" xfId="50" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
-    <cellStyle name="强调文字颜色 1 2" xfId="51" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
-    <cellStyle name="强调文字颜色 2 2" xfId="52" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
-    <cellStyle name="强调文字颜色 3 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
-    <cellStyle name="强调文字颜色 4 2" xfId="54" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
-    <cellStyle name="强调文字颜色 5 2" xfId="55" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
-    <cellStyle name="强调文字颜色 6 2" xfId="56" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
-    <cellStyle name="适中 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
-    <cellStyle name="注释 2" xfId="58" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
-    <cellStyle name="注释 2 2 2 2 3" xfId="59" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 1 10" xfId="49"/>
+    <cellStyle name="20% - 强调文字颜色 1 10 2" xfId="50"/>
+    <cellStyle name="20% - 强调文字颜色 1 10 2 4" xfId="51"/>
+    <cellStyle name="20% - 强调文字颜色 2 10" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 2 10 2" xfId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2 10 2 4" xfId="54"/>
+    <cellStyle name="20% - 强调文字颜色 3 10" xfId="55"/>
+    <cellStyle name="20% - 强调文字颜色 3 10 2" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 3 10 2 4" xfId="57"/>
+    <cellStyle name="20% - 强调文字颜色 4 10" xfId="58"/>
+    <cellStyle name="20% - 强调文字颜色 4 10 2" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 4 10 2 4" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5 10" xfId="61"/>
+    <cellStyle name="20% - 强调文字颜色 5 10 2" xfId="62"/>
+    <cellStyle name="20% - 强调文字颜色 5 10 2 4" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 6 10" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6 10 2" xfId="65"/>
+    <cellStyle name="20% - 强调文字颜色 6 10 2 4" xfId="66"/>
+    <cellStyle name="40% - 强调文字颜色 1 10" xfId="67"/>
+    <cellStyle name="40% - 强调文字颜色 2 10" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3 10" xfId="69"/>
+    <cellStyle name="40% - 强调文字颜色 4 10" xfId="70"/>
+    <cellStyle name="40% - 强调文字颜色 5 10" xfId="71"/>
+    <cellStyle name="40% - 强调文字颜色 6 10" xfId="72"/>
+    <cellStyle name="60% - 强调文字颜色 1 2" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 1 2 3" xfId="74"/>
+    <cellStyle name="60% - 强调文字颜色 2 2" xfId="75"/>
+    <cellStyle name="60% - 强调文字颜色 2 2 3" xfId="76"/>
+    <cellStyle name="60% - 强调文字颜色 3 2" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 3 2 3" xfId="78"/>
+    <cellStyle name="60% - 强调文字颜色 4 2" xfId="79"/>
+    <cellStyle name="60% - 强调文字颜色 4 2 3" xfId="80"/>
+    <cellStyle name="60% - 强调文字颜色 5 2" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 5 2 3" xfId="82"/>
+    <cellStyle name="60% - 强调文字颜色 6 2" xfId="83"/>
+    <cellStyle name="60% - 强调文字颜色 6 2 3" xfId="84"/>
+    <cellStyle name="百分比 2" xfId="85"/>
+    <cellStyle name="标题 4 2" xfId="86"/>
+    <cellStyle name="标题 5" xfId="87"/>
+    <cellStyle name="差 2" xfId="88"/>
+    <cellStyle name="常规 10" xfId="89"/>
+    <cellStyle name="常规 10 2" xfId="90"/>
+    <cellStyle name="常规 11 2" xfId="91"/>
+    <cellStyle name="常规 3" xfId="92"/>
+    <cellStyle name="常规 6" xfId="93"/>
+    <cellStyle name="常规 8" xfId="94"/>
+    <cellStyle name="超链接 2" xfId="95"/>
+    <cellStyle name="好 2" xfId="96"/>
+    <cellStyle name="解释性文本 2" xfId="97"/>
+    <cellStyle name="警告文本 2" xfId="98"/>
+    <cellStyle name="强调文字颜色 1 2" xfId="99"/>
+    <cellStyle name="强调文字颜色 2 2" xfId="100"/>
+    <cellStyle name="强调文字颜色 3 2" xfId="101"/>
+    <cellStyle name="强调文字颜色 4 2" xfId="102"/>
+    <cellStyle name="强调文字颜色 5 2" xfId="103"/>
+    <cellStyle name="强调文字颜色 6 2" xfId="104"/>
+    <cellStyle name="适中 2" xfId="105"/>
+    <cellStyle name="注释 2" xfId="106"/>
+    <cellStyle name="注释 2 2 2 2 3" xfId="107"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <i val="0"/>
       </font>
       <fill>
@@ -5195,7 +5796,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{6A4F19B7-6378-43C2-A831-56E464E4D2C8}">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{C7D681BE-04CC-451F-80E9-31D368CFBE5C}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -5203,9 +5804,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -5492,14 +6090,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Y181"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.5" customWidth="1"/>
     <col min="2" max="2" width="11.875" customWidth="1"/>
@@ -5514,7 +6112,7 @@
     <col min="15" max="15" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -5561,7 +6159,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A2" s="8" t="s">
         <v>13</v>
       </c>
@@ -5608,7 +6206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A3" s="8">
         <v>8</v>
       </c>
@@ -5655,7 +6253,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A4" s="8" t="s">
         <v>15</v>
       </c>
@@ -5702,7 +6300,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="7" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" s="7" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
@@ -5749,7 +6347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A6" s="2">
         <v>101101</v>
       </c>
@@ -5796,7 +6394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A7" s="2">
         <v>102101</v>
       </c>
@@ -5843,7 +6441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A8" s="2">
         <v>102201</v>
       </c>
@@ -5890,7 +6488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A9" s="2">
         <v>102301</v>
       </c>
@@ -5937,7 +6535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A10" s="2">
         <v>103101</v>
       </c>
@@ -5984,7 +6582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A11" s="2">
         <v>103201</v>
       </c>
@@ -6031,7 +6629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A12" s="2">
         <v>104101</v>
       </c>
@@ -6078,7 +6676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A13" s="2">
         <v>104201</v>
       </c>
@@ -6125,7 +6723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A14" s="2">
         <v>104301</v>
       </c>
@@ -6172,7 +6770,7 @@
         <v>60030001</v>
       </c>
     </row>
-    <row r="15" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A15" s="2">
         <v>104401</v>
       </c>
@@ -6219,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A16" s="2">
         <v>104501</v>
       </c>
@@ -6266,7 +6864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A17" s="2">
         <v>105101</v>
       </c>
@@ -6313,7 +6911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A18" s="2">
         <v>105201</v>
       </c>
@@ -6360,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A19" s="2">
         <v>106101</v>
       </c>
@@ -6407,7 +7005,7 @@
         <v>60030006</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A20" s="2">
         <v>106201</v>
       </c>
@@ -6454,7 +7052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A21" s="2">
         <v>106301</v>
       </c>
@@ -6501,7 +7099,7 @@
         <v>60030002</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A22" s="2">
         <v>106401</v>
       </c>
@@ -6548,7 +7146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A23" s="2">
         <v>106501</v>
       </c>
@@ -6595,7 +7193,7 @@
         <v>60030004</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A24" s="2">
         <v>107101</v>
       </c>
@@ -6642,7 +7240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A25" s="2">
         <v>107201</v>
       </c>
@@ -6689,7 +7287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A26" s="2">
         <v>107301</v>
       </c>
@@ -6736,7 +7334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A27" s="2">
         <v>108101</v>
       </c>
@@ -6783,7 +7381,7 @@
         <v>60030005</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A28" s="2">
         <v>111101</v>
       </c>
@@ -6832,7 +7430,7 @@
       <c r="Q28" s="11"/>
       <c r="R28" s="12"/>
     </row>
-    <row r="29" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A29" s="2">
         <v>112101</v>
       </c>
@@ -6881,7 +7479,7 @@
       <c r="Q29" s="13"/>
       <c r="R29" s="14"/>
     </row>
-    <row r="30" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A30" s="2">
         <v>112201</v>
       </c>
@@ -6930,7 +7528,7 @@
       <c r="Q30" s="11"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A31" s="2">
         <v>112301</v>
       </c>
@@ -6979,7 +7577,7 @@
       <c r="Q31" s="11"/>
       <c r="R31" s="1"/>
     </row>
-    <row r="32" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A32" s="2">
         <v>113101</v>
       </c>
@@ -7028,7 +7626,7 @@
       <c r="Q32" s="11"/>
       <c r="R32" s="1"/>
     </row>
-    <row r="33" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A33" s="2">
         <v>113201</v>
       </c>
@@ -7077,7 +7675,7 @@
       <c r="Q33" s="11"/>
       <c r="R33" s="1"/>
     </row>
-    <row r="34" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A34" s="2">
         <v>114101</v>
       </c>
@@ -7126,7 +7724,7 @@
       <c r="Q34" s="15"/>
       <c r="R34" s="16"/>
     </row>
-    <row r="35" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A35" s="2">
         <v>114201</v>
       </c>
@@ -7175,7 +7773,7 @@
       <c r="Q35" s="11"/>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A36" s="2">
         <v>114301</v>
       </c>
@@ -7224,7 +7822,7 @@
       <c r="Q36" s="15"/>
       <c r="R36" s="16"/>
     </row>
-    <row r="37" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A37" s="2">
         <v>114401</v>
       </c>
@@ -7273,7 +7871,7 @@
       <c r="Q37" s="11"/>
       <c r="R37" s="1"/>
     </row>
-    <row r="38" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A38" s="2">
         <v>114501</v>
       </c>
@@ -7322,7 +7920,7 @@
       <c r="Q38" s="11"/>
       <c r="R38" s="1"/>
     </row>
-    <row r="39" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A39" s="2">
         <v>115101</v>
       </c>
@@ -7371,7 +7969,7 @@
       <c r="Q39" s="11"/>
       <c r="R39" s="1"/>
     </row>
-    <row r="40" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A40" s="2">
         <v>115201</v>
       </c>
@@ -7420,7 +8018,7 @@
       <c r="Q40" s="11"/>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A41" s="2">
         <v>116101</v>
       </c>
@@ -7469,7 +8067,7 @@
       <c r="Q41" s="17"/>
       <c r="R41" s="18"/>
     </row>
-    <row r="42" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A42" s="2">
         <v>116201</v>
       </c>
@@ -7516,7 +8114,7 @@
       <c r="Q42" s="11"/>
       <c r="R42" s="1"/>
     </row>
-    <row r="43" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A43" s="2">
         <v>116301</v>
       </c>
@@ -7565,7 +8163,7 @@
       <c r="Q43" s="15"/>
       <c r="R43" s="16"/>
     </row>
-    <row r="44" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A44" s="2">
         <v>116401</v>
       </c>
@@ -7612,7 +8210,7 @@
       <c r="Q44" s="11"/>
       <c r="R44" s="1"/>
     </row>
-    <row r="45" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A45" s="2">
         <v>116501</v>
       </c>
@@ -7661,7 +8259,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="18"/>
     </row>
-    <row r="46" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A46" s="2">
         <v>117101</v>
       </c>
@@ -7710,7 +8308,7 @@
       <c r="Q46" s="20"/>
       <c r="R46" s="12"/>
     </row>
-    <row r="47" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A47" s="2">
         <v>117201</v>
       </c>
@@ -7759,7 +8357,7 @@
       <c r="Q47" s="11"/>
       <c r="R47" s="1"/>
     </row>
-    <row r="48" spans="1:18" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:18">
       <c r="A48" s="2">
         <v>117301</v>
       </c>
@@ -7808,7 +8406,7 @@
       <c r="Q48" s="11"/>
       <c r="R48" s="1"/>
     </row>
-    <row r="49" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A49" s="2">
         <v>118101</v>
       </c>
@@ -7857,7 +8455,7 @@
       <c r="Q49" s="15"/>
       <c r="R49" s="16"/>
     </row>
-    <row r="50" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A50" s="2">
         <v>201101</v>
       </c>
@@ -7904,7 +8502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A51" s="2">
         <v>202101</v>
       </c>
@@ -7948,7 +8546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A52" s="2">
         <v>202201</v>
       </c>
@@ -7992,7 +8590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A53" s="2">
         <v>202301</v>
       </c>
@@ -8039,7 +8637,7 @@
         <v>90001033</v>
       </c>
     </row>
-    <row r="54" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A54" s="2">
         <v>203101</v>
       </c>
@@ -8095,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A55" s="2">
         <v>203201</v>
       </c>
@@ -8139,7 +8737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A56" s="2">
         <v>204101</v>
       </c>
@@ -8181,7 +8779,7 @@
         <v>60030109</v>
       </c>
     </row>
-    <row r="57" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A57" s="2">
         <v>204201</v>
       </c>
@@ -8224,7 +8822,7 @@
       <c r="O57"/>
       <c r="P57"/>
     </row>
-    <row r="58" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A58" s="2">
         <v>204301</v>
       </c>
@@ -8266,7 +8864,7 @@
         <v>60030101</v>
       </c>
     </row>
-    <row r="59" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A59" s="2">
         <v>204401</v>
       </c>
@@ -8319,7 +8917,7 @@
         <v>205101</v>
       </c>
     </row>
-    <row r="60" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A60" s="2">
         <v>204501</v>
       </c>
@@ -8363,7 +8961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A61" s="2">
         <v>205101</v>
       </c>
@@ -8408,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A62" s="2">
         <v>205201</v>
       </c>
@@ -8453,7 +9051,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="63" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A63" s="2">
         <v>206101</v>
       </c>
@@ -8495,7 +9093,7 @@
         <v>60030110</v>
       </c>
     </row>
-    <row r="64" spans="1:25" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:25">
       <c r="A64" s="2">
         <v>206201</v>
       </c>
@@ -8539,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A65" s="2">
         <v>206301</v>
       </c>
@@ -8583,7 +9181,7 @@
         <v>60030102</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A66" s="2">
         <v>206401</v>
       </c>
@@ -8627,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A67" s="2">
         <v>206501</v>
       </c>
@@ -8669,7 +9267,7 @@
         <v>60030111</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A68" s="2">
         <v>207101</v>
       </c>
@@ -8713,7 +9311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A69" s="2">
         <v>207201</v>
       </c>
@@ -8757,7 +9355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A70" s="2">
         <v>207301</v>
       </c>
@@ -8801,7 +9399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A71" s="2">
         <v>208101</v>
       </c>
@@ -8845,7 +9443,7 @@
         <v>60030104</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A72" s="2">
         <v>211101</v>
       </c>
@@ -8892,7 +9490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A73" s="2">
         <v>212101</v>
       </c>
@@ -8935,7 +9533,7 @@
       </c>
       <c r="O73" s="5"/>
     </row>
-    <row r="74" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A74" s="2">
         <v>212201</v>
       </c>
@@ -8980,7 +9578,7 @@
         <v>60030105</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A75" s="2">
         <v>212301</v>
       </c>
@@ -9025,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A76" s="2">
         <v>213101</v>
       </c>
@@ -9072,7 +9670,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A77" s="2">
         <v>213201</v>
       </c>
@@ -9116,7 +9714,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A78" s="2">
         <v>214101</v>
       </c>
@@ -9161,7 +9759,7 @@
         <v>60030114</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A79" s="2">
         <v>214201</v>
       </c>
@@ -9208,7 +9806,7 @@
       <c r="P79" s="2"/>
       <c r="Q79" s="2"/>
     </row>
-    <row r="80" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A80" s="2">
         <v>214301</v>
       </c>
@@ -9255,7 +9853,7 @@
       <c r="P80" s="2"/>
       <c r="Q80" s="2"/>
     </row>
-    <row r="81" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A81" s="2">
         <v>214401</v>
       </c>
@@ -9302,7 +9900,7 @@
       <c r="P81" s="2"/>
       <c r="Q81" s="2"/>
     </row>
-    <row r="82" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A82" s="2">
         <v>214501</v>
       </c>
@@ -9349,7 +9947,7 @@
       <c r="P82" s="2"/>
       <c r="Q82" s="2"/>
     </row>
-    <row r="83" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A83" s="2">
         <v>215101</v>
       </c>
@@ -9398,7 +9996,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A84" s="2">
         <v>215201</v>
       </c>
@@ -9447,7 +10045,7 @@
       <c r="P84" s="2"/>
       <c r="Q84" s="2"/>
     </row>
-    <row r="85" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A85" s="2">
         <v>216101</v>
       </c>
@@ -9489,7 +10087,7 @@
         <v>60030110</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A86" s="2">
         <v>216201</v>
       </c>
@@ -9536,7 +10134,7 @@
       <c r="P86" s="2"/>
       <c r="Q86" s="2"/>
     </row>
-    <row r="87" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A87" s="2">
         <v>216301</v>
       </c>
@@ -9583,7 +10181,7 @@
       <c r="P87" s="2"/>
       <c r="Q87" s="2"/>
     </row>
-    <row r="88" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A88" s="2">
         <v>216401</v>
       </c>
@@ -9630,7 +10228,7 @@
       <c r="P88" s="2"/>
       <c r="Q88" s="2"/>
     </row>
-    <row r="89" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A89" s="2">
         <v>216501</v>
       </c>
@@ -9677,7 +10275,7 @@
       <c r="P89" s="2"/>
       <c r="Q89" s="2"/>
     </row>
-    <row r="90" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A90" s="2">
         <v>217101</v>
       </c>
@@ -9722,7 +10320,7 @@
       <c r="P90" s="2"/>
       <c r="Q90" s="2"/>
     </row>
-    <row r="91" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A91" s="2">
         <v>217201</v>
       </c>
@@ -9769,7 +10367,7 @@
       <c r="P91" s="2"/>
       <c r="Q91" s="2"/>
     </row>
-    <row r="92" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A92" s="2">
         <v>217301</v>
       </c>
@@ -9820,7 +10418,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" s="6" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A93" s="2">
         <v>218101</v>
       </c>
@@ -9867,7 +10465,7 @@
       <c r="P93" s="2"/>
       <c r="Q93" s="2"/>
     </row>
-    <row r="94" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A94" s="2">
         <v>301101</v>
       </c>
@@ -9914,7 +10512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A95" s="2">
         <v>302101</v>
       </c>
@@ -9959,7 +10557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:17">
       <c r="A96" s="2">
         <v>302201</v>
       </c>
@@ -10004,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A97" s="2">
         <v>302301</v>
       </c>
@@ -10049,7 +10647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A98" s="2">
         <v>303101</v>
       </c>
@@ -10095,7 +10693,7 @@
       <c r="U98" s="5"/>
       <c r="V98" s="5"/>
     </row>
-    <row r="99" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A99" s="2">
         <v>303201</v>
       </c>
@@ -10137,7 +10735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A100" s="2">
         <v>304101</v>
       </c>
@@ -10180,7 +10778,7 @@
         <v>60032001</v>
       </c>
     </row>
-    <row r="101" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A101" s="2">
         <v>304201</v>
       </c>
@@ -10225,7 +10823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A102" s="2">
         <v>304301</v>
       </c>
@@ -10268,7 +10866,7 @@
         <v>60032002</v>
       </c>
     </row>
-    <row r="103" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A103" s="2">
         <v>304401</v>
       </c>
@@ -10311,7 +10909,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="104" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A104" s="2">
         <v>304501</v>
       </c>
@@ -10356,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A105" s="2">
         <v>305101</v>
       </c>
@@ -10401,7 +10999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A106" s="2">
         <v>305201</v>
       </c>
@@ -10446,7 +11044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A107" s="2">
         <v>306101</v>
       </c>
@@ -10489,7 +11087,7 @@
       </c>
       <c r="O107" s="5"/>
     </row>
-    <row r="108" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A108" s="2">
         <v>306201</v>
       </c>
@@ -10534,7 +11132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A109" s="2">
         <v>306301</v>
       </c>
@@ -10579,7 +11177,7 @@
         <v>60032021</v>
       </c>
     </row>
-    <row r="110" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A110" s="2">
         <v>306401</v>
       </c>
@@ -10624,7 +11222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A111" s="2">
         <v>306501</v>
       </c>
@@ -10669,7 +11267,7 @@
         <v>60032005</v>
       </c>
     </row>
-    <row r="112" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:22">
       <c r="A112" s="2">
         <v>307101</v>
       </c>
@@ -10714,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A113" s="2">
         <v>307201</v>
       </c>
@@ -10761,7 +11359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A114" s="2">
         <v>307301</v>
       </c>
@@ -10804,7 +11402,7 @@
       </c>
       <c r="O114" s="5"/>
     </row>
-    <row r="115" spans="1:16" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" s="5" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A115" s="5">
         <v>308101</v>
       </c>
@@ -10849,7 +11447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A116" s="2">
         <v>311101</v>
       </c>
@@ -10894,7 +11492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A117" s="2">
         <v>312101</v>
       </c>
@@ -10939,7 +11537,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="118" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A118" s="2">
         <v>312201</v>
       </c>
@@ -10984,7 +11582,7 @@
         <v>60032101</v>
       </c>
     </row>
-    <row r="119" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A119" s="2">
         <v>312301</v>
       </c>
@@ -11029,7 +11627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A120" s="2">
         <v>313101</v>
       </c>
@@ -11074,7 +11672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A121" s="2">
         <v>313201</v>
       </c>
@@ -11119,7 +11717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A122" s="2">
         <v>314101</v>
       </c>
@@ -11164,7 +11762,7 @@
         <v>60032141</v>
       </c>
     </row>
-    <row r="123" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A123" s="2">
         <v>314201</v>
       </c>
@@ -11209,7 +11807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A124" s="2">
         <v>314301</v>
       </c>
@@ -11254,7 +11852,7 @@
         <v>60032131</v>
       </c>
     </row>
-    <row r="125" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A125" s="2">
         <v>314401</v>
       </c>
@@ -11299,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A126" s="2">
         <v>314501</v>
       </c>
@@ -11344,7 +11942,7 @@
         <v>60032151</v>
       </c>
     </row>
-    <row r="127" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A127" s="2">
         <v>315101</v>
       </c>
@@ -11389,7 +11987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:16">
       <c r="A128" s="2">
         <v>315201</v>
       </c>
@@ -11435,7 +12033,7 @@
       </c>
       <c r="P128" s="6"/>
     </row>
-    <row r="129" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A129" s="2">
         <v>316101</v>
       </c>
@@ -11480,7 +12078,7 @@
         <v>60032161</v>
       </c>
     </row>
-    <row r="130" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A130" s="2">
         <v>316201</v>
       </c>
@@ -11523,7 +12121,7 @@
       </c>
       <c r="O130" s="5"/>
     </row>
-    <row r="131" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A131" s="2">
         <v>316301</v>
       </c>
@@ -11568,7 +12166,7 @@
         <v>60032162</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A132" s="2">
         <v>316401</v>
       </c>
@@ -11613,7 +12211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A133" s="2">
         <v>316501</v>
       </c>
@@ -11656,7 +12254,7 @@
         <v>60032004</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A134" s="2">
         <v>317101</v>
       </c>
@@ -11703,7 +12301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A135" s="2">
         <v>317201</v>
       </c>
@@ -11748,7 +12346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A136" s="2">
         <v>317301</v>
       </c>
@@ -11793,7 +12391,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="137" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A137" s="2">
         <v>318101</v>
       </c>
@@ -11838,7 +12436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A138" s="2">
         <v>401101</v>
       </c>
@@ -11883,7 +12481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A139" s="2">
         <v>402101</v>
       </c>
@@ -11928,7 +12526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A140" s="2">
         <v>402201</v>
       </c>
@@ -11973,7 +12571,7 @@
         <v>60040058</v>
       </c>
     </row>
-    <row r="141" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A141" s="2">
         <v>402301</v>
       </c>
@@ -12018,7 +12616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A142" s="2">
         <v>403101</v>
       </c>
@@ -12065,7 +12663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A143" s="2">
         <v>403201</v>
       </c>
@@ -12112,7 +12710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A144" s="2">
         <v>404101</v>
       </c>
@@ -12157,7 +12755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A145" s="2">
         <v>404201</v>
       </c>
@@ -12204,7 +12802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A146" s="2">
         <v>404301</v>
       </c>
@@ -12251,7 +12849,7 @@
         <v>60040001</v>
       </c>
     </row>
-    <row r="147" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A147" s="2">
         <v>404401</v>
       </c>
@@ -12298,7 +12896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A148" s="2">
         <v>404501</v>
       </c>
@@ -12345,7 +12943,7 @@
         <v>60040002</v>
       </c>
     </row>
-    <row r="149" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A149" s="2">
         <v>405101</v>
       </c>
@@ -12392,7 +12990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A150" s="2">
         <v>405201</v>
       </c>
@@ -12437,7 +13035,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="151" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A151" s="2">
         <v>406101</v>
       </c>
@@ -12484,7 +13082,7 @@
         <v>60040060</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A152" s="2">
         <v>406201</v>
       </c>
@@ -12529,7 +13127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A153" s="2">
         <v>406301</v>
       </c>
@@ -12561,10 +13159,10 @@
         <v>1</v>
       </c>
       <c r="K153" s="2" t="s">
-        <v>594</v>
+        <v>502</v>
       </c>
       <c r="L153" s="22" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M153" s="22" t="s">
         <v>105</v>
@@ -12576,15 +13174,15 @@
         <v>60040003</v>
       </c>
     </row>
-    <row r="154" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A154" s="2">
         <v>406401</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D154" s="2">
         <v>406401</v>
@@ -12611,24 +13209,24 @@
         <v>406501</v>
       </c>
       <c r="L154" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M154" s="22" t="s">
         <v>86</v>
       </c>
       <c r="N154" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O154" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A155" s="2">
         <v>406501</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>112</v>
@@ -12658,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="L155" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M155" s="22" t="s">
         <v>112</v>
@@ -12670,15 +13268,15 @@
         <v>60040004</v>
       </c>
     </row>
-    <row r="156" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A156" s="2">
         <v>407101</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D156" s="2">
         <v>407101</v>
@@ -12705,22 +13303,22 @@
         <v>0</v>
       </c>
       <c r="L156" s="22" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="M156" s="22"/>
       <c r="N156" s="5">
         <v>0</v>
       </c>
       <c r="O156" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="157" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="157" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A157" s="2">
         <v>407201</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>120</v>
@@ -12747,10 +13345,10 @@
         <v>5</v>
       </c>
       <c r="K157" s="2" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="L157" s="22" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M157" s="22" t="s">
         <v>123</v>
@@ -12759,18 +13357,18 @@
         <v>0</v>
       </c>
       <c r="O157" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="158" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="158" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A158" s="2">
         <v>407301</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D158" s="2">
         <v>407301</v>
@@ -12797,22 +13395,22 @@
         <v>0</v>
       </c>
       <c r="L158" s="22" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M158" s="22"/>
       <c r="N158" s="5">
         <v>0</v>
       </c>
       <c r="O158" s="5" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="159" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="159" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A159" s="2">
         <v>408101</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>131</v>
@@ -12842,7 +13440,7 @@
         <v>0</v>
       </c>
       <c r="L159" s="22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M159" s="22" t="s">
         <v>133</v>
@@ -12854,7 +13452,7 @@
         <v>60040059</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A160" s="2">
         <v>411101</v>
       </c>
@@ -12862,7 +13460,7 @@
         <v>29</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D160" s="2">
         <v>411101</v>
@@ -12886,20 +13484,20 @@
         <v>3</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L160" s="22" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M160" s="22"/>
       <c r="N160" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="O160" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A161" s="2">
         <v>412101</v>
       </c>
@@ -12934,25 +13532,25 @@
         <v>413201</v>
       </c>
       <c r="L161" s="22" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M161" s="22"/>
       <c r="N161" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="O161" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A162" s="2">
         <v>412201</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D162" s="2">
         <v>412201</v>
@@ -12979,7 +13577,7 @@
         <v>414301</v>
       </c>
       <c r="L162" s="22" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M162" s="22" t="s">
         <v>148</v>
@@ -12991,7 +13589,7 @@
         <v>60040011</v>
       </c>
     </row>
-    <row r="163" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A163" s="2">
         <v>412301</v>
       </c>
@@ -13026,25 +13624,25 @@
         <v>413101</v>
       </c>
       <c r="L163" s="22" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M163" s="22"/>
       <c r="N163" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O163" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A164" s="2">
         <v>413101</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D164" s="2">
         <v>413101</v>
@@ -13071,25 +13669,25 @@
         <v>0</v>
       </c>
       <c r="L164" s="22" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M164" s="22"/>
       <c r="N164" s="5" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O164" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A165" s="2">
         <v>413201</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D165" s="2">
         <v>413201</v>
@@ -13116,25 +13714,25 @@
         <v>0</v>
       </c>
       <c r="L165" s="22" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M165" s="22"/>
       <c r="N165" s="5" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O165" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A166" s="2">
         <v>414101</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D166" s="2">
         <v>414101</v>
@@ -13161,7 +13759,7 @@
         <v>415101</v>
       </c>
       <c r="L166" s="22" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M166" s="22"/>
       <c r="N166" s="5">
@@ -13171,15 +13769,15 @@
         <v>60040012</v>
       </c>
     </row>
-    <row r="167" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A167" s="2">
         <v>414201</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D167" s="2">
         <v>414201</v>
@@ -13206,25 +13804,25 @@
         <v>414101</v>
       </c>
       <c r="L167" s="22" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M167" s="22"/>
       <c r="N167" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O167" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A168" s="2">
         <v>414301</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D168" s="2">
         <v>414301</v>
@@ -13248,10 +13846,10 @@
         <v>1</v>
       </c>
       <c r="K168" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="L168" s="22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M168" s="22" t="s">
         <v>176</v>
@@ -13263,15 +13861,15 @@
         <v>60040013</v>
       </c>
     </row>
-    <row r="169" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A169" s="2">
         <v>414401</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D169" s="2">
         <v>414401</v>
@@ -13298,17 +13896,17 @@
         <v>414501</v>
       </c>
       <c r="L169" s="22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M169" s="22"/>
       <c r="N169" s="5">
         <v>0</v>
       </c>
       <c r="O169" s="5" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="170" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="170" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A170" s="2">
         <v>414501</v>
       </c>
@@ -13316,7 +13914,7 @@
         <v>485</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D170" s="2">
         <v>414501</v>
@@ -13343,27 +13941,27 @@
         <v>415201</v>
       </c>
       <c r="L170" s="22" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M170" s="22" t="s">
         <v>185</v>
       </c>
       <c r="N170" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O170" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A171" s="2">
         <v>415101</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D171" s="2">
         <v>415101</v>
@@ -13390,7 +13988,7 @@
         <v>0</v>
       </c>
       <c r="L171" s="22" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M171" s="22" t="s">
         <v>189</v>
@@ -13399,18 +13997,18 @@
         <v>0</v>
       </c>
       <c r="O171" s="5" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="172" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="172" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A172" s="2">
         <v>415201</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D172" s="2">
         <v>415201</v>
@@ -13437,7 +14035,7 @@
         <v>0</v>
       </c>
       <c r="L172" s="22" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M172" s="22" t="s">
         <v>91</v>
@@ -13446,18 +14044,18 @@
         <v>0</v>
       </c>
       <c r="O172" s="5" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="173" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="173" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A173" s="2">
         <v>416101</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D173" s="2">
         <v>416101</v>
@@ -13484,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="L173" s="22" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M173" s="22" t="s">
         <v>193</v>
@@ -13496,15 +14094,15 @@
         <v>60040034</v>
       </c>
     </row>
-    <row r="174" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A174" s="2">
         <v>416201</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D174" s="2">
         <v>416201</v>
@@ -13531,25 +14129,25 @@
         <v>416101</v>
       </c>
       <c r="L174" s="22" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M174" s="22"/>
       <c r="N174" s="5">
         <v>0</v>
       </c>
       <c r="O174" s="5" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="175" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="175" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A175" s="2">
         <v>416301</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D175" s="2">
         <v>416301</v>
@@ -13573,20 +14171,20 @@
         <v>1</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="L175" s="22" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M175" s="22"/>
       <c r="N175" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O175" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A176" s="2">
         <v>416401</v>
       </c>
@@ -13594,7 +14192,7 @@
         <v>485</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D176" s="2">
         <v>416401</v>
@@ -13621,25 +14219,25 @@
         <v>416501</v>
       </c>
       <c r="L176" s="22" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="M176" s="22"/>
       <c r="N176" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O176" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A177" s="2">
         <v>416501</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D177" s="2">
         <v>416501</v>
@@ -13666,27 +14264,27 @@
         <v>0</v>
       </c>
       <c r="L177" s="22" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M177" s="22" t="s">
         <v>209</v>
       </c>
       <c r="N177" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="O177" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A178" s="2">
         <v>417101</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D178" s="2">
         <v>417101</v>
@@ -13713,17 +14311,17 @@
         <v>0</v>
       </c>
       <c r="L178" s="22" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M178" s="22"/>
       <c r="N178" s="5">
         <v>0</v>
       </c>
       <c r="O178" s="5" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="179" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="179" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A179" s="2">
         <v>417201</v>
       </c>
@@ -13731,7 +14329,7 @@
         <v>390</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D179" s="2">
         <v>417201</v>
@@ -13755,7 +14353,7 @@
         <v>5</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L179" s="22" t="s">
         <v>312</v>
@@ -13768,15 +14366,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A180" s="2">
         <v>417301</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D180" s="2">
         <v>417301</v>
@@ -13803,25 +14401,25 @@
         <v>0</v>
       </c>
       <c r="L180" s="22" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M180" s="22"/>
       <c r="N180" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O180" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:15" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" s="2" customFormat="1" ht="20.1" customHeight="1" spans="1:15">
       <c r="A181" s="2">
         <v>418101</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D181" s="2">
         <v>418101</v>
@@ -13848,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="L181" s="22" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M181" s="22"/>
       <c r="N181" s="5">
@@ -13859,24 +14457,25 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C3:H5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="137.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="3:8">
       <c r="C3" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>244</v>
@@ -13888,15 +14487,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="3:8">
       <c r="C5" s="3" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>244</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="F5" s="5">
         <v>0</v>
@@ -13905,7 +14504,7 @@
       <c r="H5" s="6"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>